--- a/docs/unit1/4_graphing_numsolver/(Starter-Workbook)-HW-Graphing-and-Solver.xlsx
+++ b/docs/unit1/4_graphing_numsolver/(Starter-Workbook)-HW-Graphing-and-Solver.xlsx
@@ -5,36 +5,102 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GIT_Repo\CCE_270_content\.codex_tmp_topic4\edited\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\griffizu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0966436D-E835-4460-9426-2F3B594C272D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E6B03F-3566-48E5-BF3A-1D7BE348CEB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25170" yWindow="1890" windowWidth="32775" windowHeight="20460" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Missile Launch" sheetId="4" r:id="rId1"/>
-    <sheet name="Streamflow Data" sheetId="1" r:id="rId2"/>
-    <sheet name="Summary Statistics" sheetId="2" r:id="rId3"/>
-    <sheet name="Load Calculations" sheetId="3" r:id="rId4"/>
-    <sheet name="Testing Allocation" sheetId="5" r:id="rId5"/>
+    <sheet name="Testing Allocation" sheetId="5" r:id="rId2"/>
+    <sheet name="Steel Beam Optimization" sheetId="6" r:id="rId3"/>
+    <sheet name="Wide Flange Properties" sheetId="7" r:id="rId4"/>
+    <sheet name="Streamflow Data" sheetId="1" r:id="rId5"/>
+    <sheet name="Summary Statistics" sheetId="2" r:id="rId6"/>
+    <sheet name="Load Calculations" sheetId="3" r:id="rId7"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId8"/>
+  </externalReferences>
   <definedNames>
-    <definedName name="a" localSheetId="3">'Load Calculations'!$D$15</definedName>
-    <definedName name="B" localSheetId="3">'Load Calculations'!$D$5</definedName>
-    <definedName name="d" localSheetId="3">'Load Calculations'!$H$15</definedName>
-    <definedName name="E" localSheetId="3">'Load Calculations'!$D$4</definedName>
-    <definedName name="H" localSheetId="3">'Load Calculations'!$D$6</definedName>
-    <definedName name="I" localSheetId="3">'Load Calculations'!$D$7</definedName>
-    <definedName name="L" localSheetId="3">'Load Calculations'!$D$16</definedName>
+    <definedName name="a" localSheetId="6">'Load Calculations'!$D$15</definedName>
+    <definedName name="B" localSheetId="6">'Load Calculations'!$D$5</definedName>
+    <definedName name="d" localSheetId="6">'Load Calculations'!$H$15</definedName>
+    <definedName name="E" localSheetId="6">'Load Calculations'!$D$4</definedName>
+    <definedName name="H" localSheetId="6">'Load Calculations'!$D$6</definedName>
+    <definedName name="I" localSheetId="6">'Load Calculations'!$D$7</definedName>
+    <definedName name="L" localSheetId="6">'Load Calculations'!$D$16</definedName>
     <definedName name="LOCAL_MYSQL_DATE_FORMAT" hidden="1">REPT(LOCAL_YEAR_FORMAT,4)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_MONTH_FORMAT,2)&amp;LOCAL_DATE_SEPARATOR&amp;REPT(LOCAL_DAY_FORMAT,2)&amp;" "&amp;REPT(LOCAL_HOUR_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_MINUTE_FORMAT,2)&amp;LOCAL_TIME_SEPARATOR&amp;REPT(LOCAL_SECOND_FORMAT,2)</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Wide Flange Properties'!#REF!</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Wide Flange Properties'!$A:$A</definedName>
+    <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs0" localSheetId="2" hidden="1">'Steel Beam Optimization'!$B$6</definedName>
+    <definedName name="solver_lhs1" localSheetId="2" hidden="1">'Steel Beam Optimization'!$B$19</definedName>
+    <definedName name="solver_lhs2" localSheetId="2" hidden="1">'Steel Beam Optimization'!$B$20</definedName>
+    <definedName name="solver_lhs3" localSheetId="2" hidden="1">'Steel Beam Optimization'!$B$21</definedName>
+    <definedName name="solver_lhs4" localSheetId="2" hidden="1">'Steel Beam Optimization'!$B$25</definedName>
+    <definedName name="solver_lhs5" localSheetId="2" hidden="1">'Steel Beam Optimization'!$B$6</definedName>
+    <definedName name="solver_lhs6" localSheetId="2" hidden="1">'Steel Beam Optimization'!$B$6</definedName>
+    <definedName name="solver_lhs7" localSheetId="2" hidden="1">'Steel Beam Optimization'!$B$6</definedName>
+    <definedName name="solver_lin" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="1" hidden="1">0</definedName>
+    <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">'Missile Launch'!$Q$29</definedName>
+    <definedName name="solver_opt" localSheetId="1" hidden="1">'Testing Allocation'!$C$30</definedName>
+    <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel0" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_rel1" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel3" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel4" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel5" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel6" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_rel7" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_rhs0" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rhs1" localSheetId="2" hidden="1">'Steel Beam Optimization'!$C$19</definedName>
+    <definedName name="solver_rhs2" localSheetId="2" hidden="1">'Steel Beam Optimization'!$C$20</definedName>
+    <definedName name="solver_rhs3" localSheetId="2" hidden="1">'Steel Beam Optimization'!$C$21</definedName>
+    <definedName name="solver_rhs4" localSheetId="2" hidden="1">'Steel Beam Optimization'!$C$25</definedName>
+    <definedName name="solver_rhs5" localSheetId="2" hidden="1">289</definedName>
+    <definedName name="solver_rhs6" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rhs7" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
+    <definedName name="x">'[1]Local Min Max'!$C$4</definedName>
+    <definedName name="y">'[1]Local Min Max'!$C$5</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,8 +119,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="394">
   <si>
     <t>U.S. Geological Survey Measurements of Provo River Streamflow 
 in cubic feet per second (cfs)</t>
@@ -240,6 +328,1106 @@
   <si>
     <t>Enter decision values in E5:E6. Enter formulas in F5:F6, B10:B11, and B14.</t>
   </si>
+  <si>
+    <t>Depth</t>
+  </si>
+  <si>
+    <t>Excessive Deflection</t>
+  </si>
+  <si>
+    <t>Shear Yielding in the Web</t>
+  </si>
+  <si>
+    <t>Plastic Hinge Yielding</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Unity Check</t>
+  </si>
+  <si>
+    <t>Constraints</t>
+  </si>
+  <si>
+    <t>Checks</t>
+  </si>
+  <si>
+    <t>in</t>
+  </si>
+  <si>
+    <t>Maximum</t>
+  </si>
+  <si>
+    <t>Actual</t>
+  </si>
+  <si>
+    <t>Properties</t>
+  </si>
+  <si>
+    <t>Architectural Constraints - Actual  ≤ Maximum</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>k-ft</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+  </si>
+  <si>
+    <t>Demand</t>
+  </si>
+  <si>
+    <t>Failure Mode</t>
+  </si>
+  <si>
+    <t>Structural Constraints  -  Demand  ≤  Capacity</t>
+  </si>
+  <si>
+    <r>
+      <t>in</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+  </si>
+  <si>
+    <t>Moment of Inertia, I</t>
+  </si>
+  <si>
+    <t>ksi</t>
+  </si>
+  <si>
+    <t>Modulus of Elasticity, E</t>
+  </si>
+  <si>
+    <t>k/ft</t>
+  </si>
+  <si>
+    <t>Distributed Load, w</t>
+  </si>
+  <si>
+    <t>ft</t>
+  </si>
+  <si>
+    <t>Span, L</t>
+  </si>
+  <si>
+    <r>
+      <t>Web Thickness, t</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>w</t>
+    </r>
+  </si>
+  <si>
+    <t>Depth, d</t>
+  </si>
+  <si>
+    <r>
+      <t>in</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <color rgb="FF808080"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Plastic Section Modulus, Z</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>x</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Yield Stress, F</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>y</t>
+    </r>
+  </si>
+  <si>
+    <t>lb/ft</t>
+  </si>
+  <si>
+    <t>Weight, W</t>
+  </si>
+  <si>
+    <t>Row #</t>
+  </si>
+  <si>
+    <t>W-Shape</t>
+  </si>
+  <si>
+    <t>Design Parameters</t>
+  </si>
+  <si>
+    <t>Minimize the weight of a W-shape beam subject to bending, shear, deflection, and depth limits</t>
+  </si>
+  <si>
+    <t>W4X13</t>
+  </si>
+  <si>
+    <t>W5X16</t>
+  </si>
+  <si>
+    <t>W5X19</t>
+  </si>
+  <si>
+    <t>W6X8.5</t>
+  </si>
+  <si>
+    <t>W6X9</t>
+  </si>
+  <si>
+    <t>W6X12</t>
+  </si>
+  <si>
+    <t>W6X16</t>
+  </si>
+  <si>
+    <t>W6X15</t>
+  </si>
+  <si>
+    <t>W6X20</t>
+  </si>
+  <si>
+    <t>W6X25</t>
+  </si>
+  <si>
+    <t>W8X10</t>
+  </si>
+  <si>
+    <t>W8X13</t>
+  </si>
+  <si>
+    <t>W8X15</t>
+  </si>
+  <si>
+    <t>W8X18</t>
+  </si>
+  <si>
+    <t>W8X21</t>
+  </si>
+  <si>
+    <t>W8X24</t>
+  </si>
+  <si>
+    <t>W8X28</t>
+  </si>
+  <si>
+    <t>W8X31</t>
+  </si>
+  <si>
+    <t>W8X35</t>
+  </si>
+  <si>
+    <t>W8X40</t>
+  </si>
+  <si>
+    <t>W8X48</t>
+  </si>
+  <si>
+    <t>W8X58</t>
+  </si>
+  <si>
+    <t>W8X67</t>
+  </si>
+  <si>
+    <t>W10X12</t>
+  </si>
+  <si>
+    <t>W10X15</t>
+  </si>
+  <si>
+    <t>W10X17</t>
+  </si>
+  <si>
+    <t>W10X19</t>
+  </si>
+  <si>
+    <t>W10X22</t>
+  </si>
+  <si>
+    <t>W10X26</t>
+  </si>
+  <si>
+    <t>W10X30</t>
+  </si>
+  <si>
+    <t>W10X33</t>
+  </si>
+  <si>
+    <t>W10X39</t>
+  </si>
+  <si>
+    <t>W10X45</t>
+  </si>
+  <si>
+    <t>W10X49</t>
+  </si>
+  <si>
+    <t>W10X54</t>
+  </si>
+  <si>
+    <t>W10X60</t>
+  </si>
+  <si>
+    <t>W10X68</t>
+  </si>
+  <si>
+    <t>W10X77</t>
+  </si>
+  <si>
+    <t>W10X88</t>
+  </si>
+  <si>
+    <t>W10X100</t>
+  </si>
+  <si>
+    <t>W10X112</t>
+  </si>
+  <si>
+    <t>W12X14</t>
+  </si>
+  <si>
+    <t>W12X16</t>
+  </si>
+  <si>
+    <t>W12X19</t>
+  </si>
+  <si>
+    <t>W12X22</t>
+  </si>
+  <si>
+    <t>W12X26</t>
+  </si>
+  <si>
+    <t>W12X30</t>
+  </si>
+  <si>
+    <t>W12X35</t>
+  </si>
+  <si>
+    <t>W12X40</t>
+  </si>
+  <si>
+    <t>W12X45</t>
+  </si>
+  <si>
+    <t>W12X50</t>
+  </si>
+  <si>
+    <t>W12X53</t>
+  </si>
+  <si>
+    <t>W12X58</t>
+  </si>
+  <si>
+    <t>W12X65</t>
+  </si>
+  <si>
+    <t>W12X72</t>
+  </si>
+  <si>
+    <t>W12X79</t>
+  </si>
+  <si>
+    <t>W12X87</t>
+  </si>
+  <si>
+    <t>W12X96</t>
+  </si>
+  <si>
+    <t>W12X106</t>
+  </si>
+  <si>
+    <t>W12X120</t>
+  </si>
+  <si>
+    <t>W12X136</t>
+  </si>
+  <si>
+    <t>W12X152</t>
+  </si>
+  <si>
+    <t>W12X170</t>
+  </si>
+  <si>
+    <t>W12X190</t>
+  </si>
+  <si>
+    <t>W12X210</t>
+  </si>
+  <si>
+    <t>W12X230</t>
+  </si>
+  <si>
+    <t>W12X252</t>
+  </si>
+  <si>
+    <t>W12X279</t>
+  </si>
+  <si>
+    <t>W12X305</t>
+  </si>
+  <si>
+    <t>W12X336</t>
+  </si>
+  <si>
+    <t>W14X22</t>
+  </si>
+  <si>
+    <t>W14X26</t>
+  </si>
+  <si>
+    <t>W14X30</t>
+  </si>
+  <si>
+    <t>W14X34</t>
+  </si>
+  <si>
+    <t>W14X38</t>
+  </si>
+  <si>
+    <t>W14X43</t>
+  </si>
+  <si>
+    <t>W14X48</t>
+  </si>
+  <si>
+    <t>W14X53</t>
+  </si>
+  <si>
+    <t>W14X61</t>
+  </si>
+  <si>
+    <t>W14X68</t>
+  </si>
+  <si>
+    <t>W14X74</t>
+  </si>
+  <si>
+    <t>W14X82</t>
+  </si>
+  <si>
+    <t>W14X90</t>
+  </si>
+  <si>
+    <t>W14X99</t>
+  </si>
+  <si>
+    <t>W14X109</t>
+  </si>
+  <si>
+    <t>W14X120</t>
+  </si>
+  <si>
+    <t>W14X132</t>
+  </si>
+  <si>
+    <t>W14X145</t>
+  </si>
+  <si>
+    <t>W14X159</t>
+  </si>
+  <si>
+    <t>W14X176</t>
+  </si>
+  <si>
+    <t>W14X193</t>
+  </si>
+  <si>
+    <t>W14X211</t>
+  </si>
+  <si>
+    <t>W14X233</t>
+  </si>
+  <si>
+    <t>W14X257</t>
+  </si>
+  <si>
+    <t>W14X283</t>
+  </si>
+  <si>
+    <t>W14X311</t>
+  </si>
+  <si>
+    <t>W14X342</t>
+  </si>
+  <si>
+    <t>W14X370</t>
+  </si>
+  <si>
+    <t>W14X398</t>
+  </si>
+  <si>
+    <t>W14X426</t>
+  </si>
+  <si>
+    <t>W14X455</t>
+  </si>
+  <si>
+    <t>W14X500</t>
+  </si>
+  <si>
+    <t>W14X550</t>
+  </si>
+  <si>
+    <t>W14X605</t>
+  </si>
+  <si>
+    <t>W14X665</t>
+  </si>
+  <si>
+    <t>W14X730</t>
+  </si>
+  <si>
+    <t>W14X808</t>
+  </si>
+  <si>
+    <t>W14X873</t>
+  </si>
+  <si>
+    <t>W16X26</t>
+  </si>
+  <si>
+    <t>W16X31</t>
+  </si>
+  <si>
+    <t>W16X36</t>
+  </si>
+  <si>
+    <t>W16X40</t>
+  </si>
+  <si>
+    <t>W16X45</t>
+  </si>
+  <si>
+    <t>W16X50</t>
+  </si>
+  <si>
+    <t>W16X57</t>
+  </si>
+  <si>
+    <t>W16X67</t>
+  </si>
+  <si>
+    <t>W16X77</t>
+  </si>
+  <si>
+    <t>W16X89</t>
+  </si>
+  <si>
+    <t>W16X100</t>
+  </si>
+  <si>
+    <t>W18X35</t>
+  </si>
+  <si>
+    <t>W18X40</t>
+  </si>
+  <si>
+    <t>W18X46</t>
+  </si>
+  <si>
+    <t>W18X50</t>
+  </si>
+  <si>
+    <t>W18X55</t>
+  </si>
+  <si>
+    <t>W18X60</t>
+  </si>
+  <si>
+    <t>W18X65</t>
+  </si>
+  <si>
+    <t>W18X71</t>
+  </si>
+  <si>
+    <t>W18X76</t>
+  </si>
+  <si>
+    <t>W18X86</t>
+  </si>
+  <si>
+    <t>W18X97</t>
+  </si>
+  <si>
+    <t>W18X106</t>
+  </si>
+  <si>
+    <t>W18X119</t>
+  </si>
+  <si>
+    <t>W18X130</t>
+  </si>
+  <si>
+    <t>W18X143</t>
+  </si>
+  <si>
+    <t>W18X158</t>
+  </si>
+  <si>
+    <t>W18X175</t>
+  </si>
+  <si>
+    <t>W18X192</t>
+  </si>
+  <si>
+    <t>W18X211</t>
+  </si>
+  <si>
+    <t>W18X234</t>
+  </si>
+  <si>
+    <t>W18X258</t>
+  </si>
+  <si>
+    <t>W18X283</t>
+  </si>
+  <si>
+    <t>W18X311</t>
+  </si>
+  <si>
+    <t>W21X44</t>
+  </si>
+  <si>
+    <t>W21X50</t>
+  </si>
+  <si>
+    <t>W21X57</t>
+  </si>
+  <si>
+    <t>W21X48</t>
+  </si>
+  <si>
+    <t>W21X55</t>
+  </si>
+  <si>
+    <t>W21X62</t>
+  </si>
+  <si>
+    <t>W21X68</t>
+  </si>
+  <si>
+    <t>W21X73</t>
+  </si>
+  <si>
+    <t>W21X83</t>
+  </si>
+  <si>
+    <t>W21X93</t>
+  </si>
+  <si>
+    <t>W21X101</t>
+  </si>
+  <si>
+    <t>W21X111</t>
+  </si>
+  <si>
+    <t>W21X122</t>
+  </si>
+  <si>
+    <t>W21X132</t>
+  </si>
+  <si>
+    <t>W21X147</t>
+  </si>
+  <si>
+    <t>W21X166</t>
+  </si>
+  <si>
+    <t>W21X182</t>
+  </si>
+  <si>
+    <t>W21X201</t>
+  </si>
+  <si>
+    <t>W21X223</t>
+  </si>
+  <si>
+    <t>W21X248</t>
+  </si>
+  <si>
+    <t>W21X275</t>
+  </si>
+  <si>
+    <t>W24X55</t>
+  </si>
+  <si>
+    <t>W24X62</t>
+  </si>
+  <si>
+    <t>W24X68</t>
+  </si>
+  <si>
+    <t>W24X76</t>
+  </si>
+  <si>
+    <t>W24X84</t>
+  </si>
+  <si>
+    <t>W24X94</t>
+  </si>
+  <si>
+    <t>W24X103</t>
+  </si>
+  <si>
+    <t>W24X104</t>
+  </si>
+  <si>
+    <t>W24X117</t>
+  </si>
+  <si>
+    <t>W24X131</t>
+  </si>
+  <si>
+    <t>W24X146</t>
+  </si>
+  <si>
+    <t>W24X162</t>
+  </si>
+  <si>
+    <t>W24X176</t>
+  </si>
+  <si>
+    <t>W24X192</t>
+  </si>
+  <si>
+    <t>W24X207</t>
+  </si>
+  <si>
+    <t>W24X229</t>
+  </si>
+  <si>
+    <t>W24X250</t>
+  </si>
+  <si>
+    <t>W24X279</t>
+  </si>
+  <si>
+    <t>W24X306</t>
+  </si>
+  <si>
+    <t>W24X335</t>
+  </si>
+  <si>
+    <t>W24X370</t>
+  </si>
+  <si>
+    <t>W27X84</t>
+  </si>
+  <si>
+    <t>W27X94</t>
+  </si>
+  <si>
+    <t>W27X102</t>
+  </si>
+  <si>
+    <t>W27X114</t>
+  </si>
+  <si>
+    <t>W27X129</t>
+  </si>
+  <si>
+    <t>W27X146</t>
+  </si>
+  <si>
+    <t>W27X161</t>
+  </si>
+  <si>
+    <t>W27X178</t>
+  </si>
+  <si>
+    <t>W27X194</t>
+  </si>
+  <si>
+    <t>W27X217</t>
+  </si>
+  <si>
+    <t>W27X235</t>
+  </si>
+  <si>
+    <t>W27X258</t>
+  </si>
+  <si>
+    <t>W27X281</t>
+  </si>
+  <si>
+    <t>W27X307</t>
+  </si>
+  <si>
+    <t>W27X336</t>
+  </si>
+  <si>
+    <t>W27X368</t>
+  </si>
+  <si>
+    <t>W27X539</t>
+  </si>
+  <si>
+    <t>W30X90</t>
+  </si>
+  <si>
+    <t>W30X99</t>
+  </si>
+  <si>
+    <t>W30X108</t>
+  </si>
+  <si>
+    <t>W30X116</t>
+  </si>
+  <si>
+    <t>W30X124</t>
+  </si>
+  <si>
+    <t>W30X132</t>
+  </si>
+  <si>
+    <t>W30X148</t>
+  </si>
+  <si>
+    <t>W30X173</t>
+  </si>
+  <si>
+    <t>W30X191</t>
+  </si>
+  <si>
+    <t>W30X211</t>
+  </si>
+  <si>
+    <t>W30X235</t>
+  </si>
+  <si>
+    <t>W30X261</t>
+  </si>
+  <si>
+    <t>W30X292</t>
+  </si>
+  <si>
+    <t>W30X326</t>
+  </si>
+  <si>
+    <t>W30X357</t>
+  </si>
+  <si>
+    <t>W30X391</t>
+  </si>
+  <si>
+    <t>W33X118</t>
+  </si>
+  <si>
+    <t>W33X130</t>
+  </si>
+  <si>
+    <t>W33X141</t>
+  </si>
+  <si>
+    <t>W33X152</t>
+  </si>
+  <si>
+    <t>W33X169</t>
+  </si>
+  <si>
+    <t>W33X201</t>
+  </si>
+  <si>
+    <t>W33X221</t>
+  </si>
+  <si>
+    <t>W33X241</t>
+  </si>
+  <si>
+    <t>W33X263</t>
+  </si>
+  <si>
+    <t>W33X291</t>
+  </si>
+  <si>
+    <t>W33X318</t>
+  </si>
+  <si>
+    <t>W33X354</t>
+  </si>
+  <si>
+    <t>W33X387</t>
+  </si>
+  <si>
+    <t>W36X135</t>
+  </si>
+  <si>
+    <t>W36X150</t>
+  </si>
+  <si>
+    <t>W36X160</t>
+  </si>
+  <si>
+    <t>W36X170</t>
+  </si>
+  <si>
+    <t>W36X182</t>
+  </si>
+  <si>
+    <t>W36X194</t>
+  </si>
+  <si>
+    <t>W36X210</t>
+  </si>
+  <si>
+    <t>W36X232</t>
+  </si>
+  <si>
+    <t>W36X256</t>
+  </si>
+  <si>
+    <t>W36X286</t>
+  </si>
+  <si>
+    <t>W36X318</t>
+  </si>
+  <si>
+    <t>W36X350</t>
+  </si>
+  <si>
+    <t>W36X387</t>
+  </si>
+  <si>
+    <t>W36X231</t>
+  </si>
+  <si>
+    <t>W36X247</t>
+  </si>
+  <si>
+    <t>W36X262</t>
+  </si>
+  <si>
+    <t>W36X282</t>
+  </si>
+  <si>
+    <t>W36X302</t>
+  </si>
+  <si>
+    <t>W36X330</t>
+  </si>
+  <si>
+    <t>W36X361</t>
+  </si>
+  <si>
+    <t>W36X395</t>
+  </si>
+  <si>
+    <t>W36X441</t>
+  </si>
+  <si>
+    <t>W36X487</t>
+  </si>
+  <si>
+    <t>W36X529</t>
+  </si>
+  <si>
+    <t>W36X652</t>
+  </si>
+  <si>
+    <t>W36X723</t>
+  </si>
+  <si>
+    <t>W36X802</t>
+  </si>
+  <si>
+    <t>W36X853</t>
+  </si>
+  <si>
+    <t>W36X925</t>
+  </si>
+  <si>
+    <t>W40X149</t>
+  </si>
+  <si>
+    <t>W40X167</t>
+  </si>
+  <si>
+    <t>W40X183</t>
+  </si>
+  <si>
+    <t>W40X211</t>
+  </si>
+  <si>
+    <t>W40X235</t>
+  </si>
+  <si>
+    <t>W40X264</t>
+  </si>
+  <si>
+    <t>W40X278</t>
+  </si>
+  <si>
+    <t>W40X294</t>
+  </si>
+  <si>
+    <t>W40X277</t>
+  </si>
+  <si>
+    <t>W40X331</t>
+  </si>
+  <si>
+    <t>W40X392</t>
+  </si>
+  <si>
+    <t>W40X199</t>
+  </si>
+  <si>
+    <t>W40X215</t>
+  </si>
+  <si>
+    <t>W40X249</t>
+  </si>
+  <si>
+    <t>W40X297</t>
+  </si>
+  <si>
+    <t>W40X324</t>
+  </si>
+  <si>
+    <t>W40X362</t>
+  </si>
+  <si>
+    <t>W40X372</t>
+  </si>
+  <si>
+    <t>W40X397</t>
+  </si>
+  <si>
+    <t>W40X431</t>
+  </si>
+  <si>
+    <t>W40X503</t>
+  </si>
+  <si>
+    <t>W40X593</t>
+  </si>
+  <si>
+    <t>W40X655</t>
+  </si>
+  <si>
+    <t>W44X230</t>
+  </si>
+  <si>
+    <t>W44X262</t>
+  </si>
+  <si>
+    <t>W44X290</t>
+  </si>
+  <si>
+    <t>W44X335</t>
+  </si>
+  <si>
+    <t>W44X368</t>
+  </si>
+  <si>
+    <t>W44X408</t>
+  </si>
+  <si>
+    <r>
+      <t>Z</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>x</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>x</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>w</t>
+    </r>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>Wide Flange Shape</t>
+  </si>
+  <si>
+    <t>Wide-Flange Beam Shape Optimization</t>
+  </si>
 </sst>
 </file>
 
@@ -251,11 +1439,18 @@
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="46" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -452,8 +1647,122 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <vertAlign val="superscript"/>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF595959"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <vertAlign val="subscript"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -538,8 +1847,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -712,178 +2033,326 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="7"/>
+    <xf numFmtId="9" fontId="33" fillId="0" borderId="7" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="24" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="28" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="24" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="24" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="24" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="2"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="7" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="34" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="7" xfId="2" applyFont="1"/>
+    <xf numFmtId="1" fontId="32" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="32" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="7" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="4"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="7" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="39" fillId="16" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="39" fillId="16" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="7" xfId="5" applyFont="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="7" xfId="5" applyFont="1"/>
+    <xf numFmtId="2" fontId="34" fillId="0" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="34" fillId="0" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="34" fillId="0" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="7" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="34" fillId="0" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="12" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="7" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="7" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="23" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="23" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="27" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="23" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="23" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="23" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{5676C250-07F4-43D0-9963-F8A8FEB63B91}"/>
+    <cellStyle name="Normal 2 2" xfId="5" xr:uid="{4DA4A5BB-F470-4CA2-837B-A1EAC6139471}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{30B6EA64-57A8-4F9C-9395-DBECA46ADC5D}"/>
+    <cellStyle name="Normal 4" xfId="4" xr:uid="{5B26A37D-FB74-4BDF-884A-8EC80D3A915C}"/>
+    <cellStyle name="Percent 2" xfId="3" xr:uid="{5C3E4A12-AC7D-49C8-90A1-56CDFC0FDEF5}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color theme="7"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFB7B7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -5821,6 +7290,122 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>444501</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>55564</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>55564</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>33338</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65035093-D129-4F1E-8CBA-6B84BBE37436}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6835776" y="1960564"/>
+          <a:ext cx="192088" cy="168274"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="1500" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5249008" cy="2143424"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65DEB49B-D043-4C89-A443-BB577899FE3E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5867400" y="857250"/>
+          <a:ext cx="5249008" cy="2143424"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
@@ -5858,7 +7443,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -6629,6 +8214,32 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Local Min Max"/>
+      <sheetName val="Steel Beam Optimization"/>
+      <sheetName val="Wide Flange Properties"/>
+      <sheetName val="Claude Question"/>
+      <sheetName val="Claude Setup"/>
+      <sheetName val="Claude Answer Key"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -6931,6 +8542,6365 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E99BCD4C-E58D-42DD-8328-AD2B9CAF67CB}">
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="27.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="3" max="4" width="19.7109375" customWidth="1"/>
+    <col min="5" max="6" width="17.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="62" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+    </row>
+    <row r="3" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A3" s="60"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="60"/>
+    </row>
+    <row r="4" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="63" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="63" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="63" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="63" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A5" s="64" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="66">
+        <v>220</v>
+      </c>
+      <c r="C5" s="69">
+        <v>3</v>
+      </c>
+      <c r="D5" s="69">
+        <v>2</v>
+      </c>
+      <c r="E5" s="70"/>
+      <c r="F5" s="67"/>
+    </row>
+    <row r="6" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A6" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="66">
+        <v>150</v>
+      </c>
+      <c r="C6" s="69">
+        <v>2</v>
+      </c>
+      <c r="D6" s="69">
+        <v>3</v>
+      </c>
+      <c r="E6" s="70"/>
+      <c r="F6" s="67"/>
+    </row>
+    <row r="7" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A7" s="60"/>
+      <c r="B7" s="60"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="60"/>
+    </row>
+    <row r="8" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A8" s="60"/>
+      <c r="B8" s="60"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
+      <c r="F8" s="60"/>
+    </row>
+    <row r="9" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A9" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="63" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="63" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
+      <c r="F9" s="60"/>
+    </row>
+    <row r="10" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A10" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="71"/>
+      <c r="C10" s="69">
+        <v>120</v>
+      </c>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+    </row>
+    <row r="11" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A11" s="64" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="71"/>
+      <c r="C11" s="69">
+        <v>120</v>
+      </c>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+    </row>
+    <row r="12" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A12" s="60"/>
+      <c r="B12" s="60"/>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+    </row>
+    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="60"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="65" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="68"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+    </row>
+    <row r="15" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A15" s="60"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+    </row>
+    <row r="16" spans="1:6" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A16" s="72" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="72"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="72"/>
+      <c r="E16" s="72"/>
+      <c r="F16" s="72"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{106BD11F-61B5-43E9-B9F8-F4A59C7D221E}">
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="33.85546875" style="73" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="73" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" style="73" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" style="73" customWidth="1"/>
+    <col min="5" max="16384" width="8.7109375" style="73"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="102" t="s">
+        <v>393</v>
+      </c>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="103" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="101" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="101"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="85" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="91" t="str" cm="1">
+        <f t="array" ref="B5">INDEX('Wide Flange Properties'!A1:A290,'Steel Beam Optimization'!B6)</f>
+        <v>W44X408</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="88" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="88" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="89"/>
+      <c r="C7" s="80" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A8" s="88" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" s="84">
+        <v>50</v>
+      </c>
+      <c r="C8" s="80" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A9" s="88" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="84"/>
+      <c r="C9" s="87" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="88" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="89"/>
+      <c r="C10" s="87" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A11" s="88" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="84"/>
+      <c r="C11" s="87" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="86"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="85" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" s="84">
+        <v>20</v>
+      </c>
+      <c r="C12" s="80" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="85" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="84">
+        <v>2</v>
+      </c>
+      <c r="C13" s="80" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="85" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="84">
+        <v>29000</v>
+      </c>
+      <c r="C14" s="80" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="85" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="84"/>
+      <c r="C15" s="80" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="101" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="101"/>
+      <c r="C17" s="101"/>
+      <c r="D17" s="101"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="78" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="78" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="78" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="77" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="82"/>
+      <c r="C19" s="82">
+        <f>0.9*B8*B9/12</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="80" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="77" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="82"/>
+      <c r="C20" s="81">
+        <f>B10*B11*0.6*B8</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="80" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="77" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" s="83"/>
+      <c r="C21" s="83">
+        <f>B12*12/360</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D21" s="80" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="101" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="101"/>
+      <c r="C23" s="101"/>
+      <c r="D23" s="101"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="78" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="78" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="78" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="82">
+        <f>B10</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="81">
+        <v>13</v>
+      </c>
+      <c r="D25" s="80" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="101" t="s">
+        <v>68</v>
+      </c>
+      <c r="B27" s="101"/>
+      <c r="C27" s="101"/>
+      <c r="D27" s="101"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="79" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="78" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="78" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="77" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" s="76" t="e">
+        <f>B19/C19</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C29" s="75" t="str">
+        <f>IF(B19&lt;=C19,"OK","NOT GOOD")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="77" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="76" t="e">
+        <f>B20/C20</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C30" s="75" t="str">
+        <f>IF(B20&lt;=C20,"OK","NOT GOOD")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="77" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="76">
+        <f>B21/C21</f>
+        <v>0</v>
+      </c>
+      <c r="C31" s="75" t="str">
+        <f>IF(B21&lt;=C21,"OK","NOT GOOD")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="76">
+        <f>B25/C25</f>
+        <v>0</v>
+      </c>
+      <c r="C32" s="75" t="str">
+        <f>IF(B25&lt;=C25,"OK","NOT GOOD")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="74"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="74"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A23:D23"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C29:C32">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$C29="NOT GOOD"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>$C29="OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75505EF-6D17-429C-B2D8-183E4137BECA}">
+  <dimension ref="A1:F292"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="26.42578125" style="92" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="9.140625" style="92" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="92"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="100" t="s">
+        <v>392</v>
+      </c>
+      <c r="B1" s="99" t="s">
+        <v>391</v>
+      </c>
+      <c r="C1" s="99" t="s">
+        <v>390</v>
+      </c>
+      <c r="D1" s="99" t="s">
+        <v>389</v>
+      </c>
+      <c r="E1" s="99" t="s">
+        <v>388</v>
+      </c>
+      <c r="F1" s="99" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="97" t="s">
+        <v>386</v>
+      </c>
+      <c r="B2" s="98">
+        <v>408</v>
+      </c>
+      <c r="C2" s="95">
+        <v>44.8</v>
+      </c>
+      <c r="D2" s="94">
+        <v>1.22</v>
+      </c>
+      <c r="E2" s="98">
+        <v>38700</v>
+      </c>
+      <c r="F2" s="98">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="97" t="s">
+        <v>385</v>
+      </c>
+      <c r="B3" s="98">
+        <v>368</v>
+      </c>
+      <c r="C3" s="95">
+        <v>44.4</v>
+      </c>
+      <c r="D3" s="94">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E3" s="98">
+        <v>34700</v>
+      </c>
+      <c r="F3" s="98">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="97" t="s">
+        <v>384</v>
+      </c>
+      <c r="B4" s="98">
+        <v>335</v>
+      </c>
+      <c r="C4" s="95">
+        <v>44</v>
+      </c>
+      <c r="D4" s="96">
+        <v>1.03</v>
+      </c>
+      <c r="E4" s="98">
+        <v>31100</v>
+      </c>
+      <c r="F4" s="98">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="97" t="s">
+        <v>383</v>
+      </c>
+      <c r="B5" s="98">
+        <v>290</v>
+      </c>
+      <c r="C5" s="95">
+        <v>43.6</v>
+      </c>
+      <c r="D5" s="96">
+        <v>0.86499999999999999</v>
+      </c>
+      <c r="E5" s="98">
+        <v>27000</v>
+      </c>
+      <c r="F5" s="98">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="97" t="s">
+        <v>382</v>
+      </c>
+      <c r="B6" s="98">
+        <v>262</v>
+      </c>
+      <c r="C6" s="95">
+        <v>43.3</v>
+      </c>
+      <c r="D6" s="96">
+        <v>0.78500000000000003</v>
+      </c>
+      <c r="E6" s="98">
+        <v>24100</v>
+      </c>
+      <c r="F6" s="98">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="97" t="s">
+        <v>381</v>
+      </c>
+      <c r="B7" s="98">
+        <v>230</v>
+      </c>
+      <c r="C7" s="95">
+        <v>42.9</v>
+      </c>
+      <c r="D7" s="96">
+        <v>0.71</v>
+      </c>
+      <c r="E7" s="98">
+        <v>20800</v>
+      </c>
+      <c r="F7" s="98">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="97" t="s">
+        <v>380</v>
+      </c>
+      <c r="B8" s="98">
+        <v>655</v>
+      </c>
+      <c r="C8" s="95">
+        <v>43.6</v>
+      </c>
+      <c r="D8" s="94">
+        <v>1.97</v>
+      </c>
+      <c r="E8" s="98">
+        <v>56500</v>
+      </c>
+      <c r="F8" s="98">
+        <v>3080</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="97" t="s">
+        <v>379</v>
+      </c>
+      <c r="B9" s="98">
+        <v>593</v>
+      </c>
+      <c r="C9" s="95">
+        <v>43</v>
+      </c>
+      <c r="D9" s="94">
+        <v>1.79</v>
+      </c>
+      <c r="E9" s="98">
+        <v>50400</v>
+      </c>
+      <c r="F9" s="98">
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="97" t="s">
+        <v>378</v>
+      </c>
+      <c r="B10" s="98">
+        <v>503</v>
+      </c>
+      <c r="C10" s="95">
+        <v>42.1</v>
+      </c>
+      <c r="D10" s="94">
+        <v>1.54</v>
+      </c>
+      <c r="E10" s="98">
+        <v>41600</v>
+      </c>
+      <c r="F10" s="98">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="97" t="s">
+        <v>377</v>
+      </c>
+      <c r="B11" s="98">
+        <v>431</v>
+      </c>
+      <c r="C11" s="95">
+        <v>41.3</v>
+      </c>
+      <c r="D11" s="94">
+        <v>1.34</v>
+      </c>
+      <c r="E11" s="98">
+        <v>34800</v>
+      </c>
+      <c r="F11" s="98">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="97" t="s">
+        <v>376</v>
+      </c>
+      <c r="B12" s="98">
+        <v>397</v>
+      </c>
+      <c r="C12" s="95">
+        <v>41</v>
+      </c>
+      <c r="D12" s="94">
+        <v>1.22</v>
+      </c>
+      <c r="E12" s="98">
+        <v>32000</v>
+      </c>
+      <c r="F12" s="98">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="97" t="s">
+        <v>375</v>
+      </c>
+      <c r="B13" s="98">
+        <v>372</v>
+      </c>
+      <c r="C13" s="95">
+        <v>40.6</v>
+      </c>
+      <c r="D13" s="94">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="E13" s="98">
+        <v>29600</v>
+      </c>
+      <c r="F13" s="98">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="97" t="s">
+        <v>374</v>
+      </c>
+      <c r="B14" s="98">
+        <v>362</v>
+      </c>
+      <c r="C14" s="95">
+        <v>40.6</v>
+      </c>
+      <c r="D14" s="94">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="E14" s="98">
+        <v>28900</v>
+      </c>
+      <c r="F14" s="98">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="97" t="s">
+        <v>373</v>
+      </c>
+      <c r="B15" s="98">
+        <v>324</v>
+      </c>
+      <c r="C15" s="95">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="D15" s="94">
+        <v>1</v>
+      </c>
+      <c r="E15" s="98">
+        <v>25600</v>
+      </c>
+      <c r="F15" s="98">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="97" t="s">
+        <v>372</v>
+      </c>
+      <c r="B16" s="98">
+        <v>297</v>
+      </c>
+      <c r="C16" s="95">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="D16" s="96">
+        <v>0.93</v>
+      </c>
+      <c r="E16" s="98">
+        <v>23200</v>
+      </c>
+      <c r="F16" s="98">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="97" t="s">
+        <v>366</v>
+      </c>
+      <c r="B17" s="98">
+        <v>277</v>
+      </c>
+      <c r="C17" s="95">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="D17" s="96">
+        <v>0.83</v>
+      </c>
+      <c r="E17" s="98">
+        <v>21900</v>
+      </c>
+      <c r="F17" s="98">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="97" t="s">
+        <v>371</v>
+      </c>
+      <c r="B18" s="98">
+        <v>249</v>
+      </c>
+      <c r="C18" s="95">
+        <v>39.4</v>
+      </c>
+      <c r="D18" s="96">
+        <v>0.75</v>
+      </c>
+      <c r="E18" s="98">
+        <v>19600</v>
+      </c>
+      <c r="F18" s="98">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="97" t="s">
+        <v>370</v>
+      </c>
+      <c r="B19" s="98">
+        <v>215</v>
+      </c>
+      <c r="C19" s="95">
+        <v>39</v>
+      </c>
+      <c r="D19" s="96">
+        <v>0.65</v>
+      </c>
+      <c r="E19" s="98">
+        <v>16700</v>
+      </c>
+      <c r="F19" s="98">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="97" t="s">
+        <v>369</v>
+      </c>
+      <c r="B20" s="98">
+        <v>199</v>
+      </c>
+      <c r="C20" s="95">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="D20" s="96">
+        <v>0.65</v>
+      </c>
+      <c r="E20" s="98">
+        <v>14900</v>
+      </c>
+      <c r="F20" s="98">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="97" t="s">
+        <v>368</v>
+      </c>
+      <c r="B21" s="98">
+        <v>392</v>
+      </c>
+      <c r="C21" s="95">
+        <v>41.6</v>
+      </c>
+      <c r="D21" s="94">
+        <v>1.42</v>
+      </c>
+      <c r="E21" s="98">
+        <v>29900</v>
+      </c>
+      <c r="F21" s="98">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="97" t="s">
+        <v>367</v>
+      </c>
+      <c r="B22" s="98">
+        <v>331</v>
+      </c>
+      <c r="C22" s="95">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="D22" s="94">
+        <v>1.22</v>
+      </c>
+      <c r="E22" s="98">
+        <v>24700</v>
+      </c>
+      <c r="F22" s="98">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="97" t="s">
+        <v>366</v>
+      </c>
+      <c r="B23" s="98">
+        <v>327</v>
+      </c>
+      <c r="C23" s="95">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="D23" s="94">
+        <v>1.18</v>
+      </c>
+      <c r="E23" s="98">
+        <v>24500</v>
+      </c>
+      <c r="F23" s="98">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="97" t="s">
+        <v>365</v>
+      </c>
+      <c r="B24" s="98">
+        <v>294</v>
+      </c>
+      <c r="C24" s="95">
+        <v>40.4</v>
+      </c>
+      <c r="D24" s="94">
+        <v>1.06</v>
+      </c>
+      <c r="E24" s="98">
+        <v>21900</v>
+      </c>
+      <c r="F24" s="98">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="97" t="s">
+        <v>364</v>
+      </c>
+      <c r="B25" s="98">
+        <v>278</v>
+      </c>
+      <c r="C25" s="95">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="D25" s="94">
+        <v>1.03</v>
+      </c>
+      <c r="E25" s="98">
+        <v>20500</v>
+      </c>
+      <c r="F25" s="98">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="97" t="s">
+        <v>363</v>
+      </c>
+      <c r="B26" s="98">
+        <v>264</v>
+      </c>
+      <c r="C26" s="95">
+        <v>40</v>
+      </c>
+      <c r="D26" s="96">
+        <v>0.96</v>
+      </c>
+      <c r="E26" s="98">
+        <v>19400</v>
+      </c>
+      <c r="F26" s="98">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="97" t="s">
+        <v>362</v>
+      </c>
+      <c r="B27" s="98">
+        <v>235</v>
+      </c>
+      <c r="C27" s="95">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="D27" s="96">
+        <v>0.83</v>
+      </c>
+      <c r="E27" s="98">
+        <v>17400</v>
+      </c>
+      <c r="F27" s="98">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="97" t="s">
+        <v>361</v>
+      </c>
+      <c r="B28" s="98">
+        <v>211</v>
+      </c>
+      <c r="C28" s="95">
+        <v>39.4</v>
+      </c>
+      <c r="D28" s="96">
+        <v>0.75</v>
+      </c>
+      <c r="E28" s="98">
+        <v>15500</v>
+      </c>
+      <c r="F28" s="98">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="97" t="s">
+        <v>360</v>
+      </c>
+      <c r="B29" s="98">
+        <v>183</v>
+      </c>
+      <c r="C29" s="95">
+        <v>39</v>
+      </c>
+      <c r="D29" s="96">
+        <v>0.65</v>
+      </c>
+      <c r="E29" s="98">
+        <v>13200</v>
+      </c>
+      <c r="F29" s="98">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="97" t="s">
+        <v>359</v>
+      </c>
+      <c r="B30" s="98">
+        <v>167</v>
+      </c>
+      <c r="C30" s="95">
+        <v>38.6</v>
+      </c>
+      <c r="D30" s="96">
+        <v>0.65</v>
+      </c>
+      <c r="E30" s="98">
+        <v>11600</v>
+      </c>
+      <c r="F30" s="98">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="97" t="s">
+        <v>358</v>
+      </c>
+      <c r="B31" s="98">
+        <v>149</v>
+      </c>
+      <c r="C31" s="95">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="D31" s="96">
+        <v>0.63</v>
+      </c>
+      <c r="E31" s="98">
+        <v>9800</v>
+      </c>
+      <c r="F31" s="98">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="97" t="s">
+        <v>357</v>
+      </c>
+      <c r="B32" s="98">
+        <v>925</v>
+      </c>
+      <c r="C32" s="95">
+        <v>43.1</v>
+      </c>
+      <c r="D32" s="94">
+        <v>3.02</v>
+      </c>
+      <c r="E32" s="98">
+        <v>73000</v>
+      </c>
+      <c r="F32" s="98">
+        <v>4130</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" s="97" t="s">
+        <v>356</v>
+      </c>
+      <c r="B33" s="98">
+        <v>853</v>
+      </c>
+      <c r="C33" s="95">
+        <v>43.1</v>
+      </c>
+      <c r="D33" s="94">
+        <v>2.52</v>
+      </c>
+      <c r="E33" s="98">
+        <v>70000</v>
+      </c>
+      <c r="F33" s="98">
+        <v>3920</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" s="97" t="s">
+        <v>355</v>
+      </c>
+      <c r="B34" s="98">
+        <v>802</v>
+      </c>
+      <c r="C34" s="95">
+        <v>42.6</v>
+      </c>
+      <c r="D34" s="94">
+        <v>2.38</v>
+      </c>
+      <c r="E34" s="98">
+        <v>64800</v>
+      </c>
+      <c r="F34" s="98">
+        <v>3660</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="97" t="s">
+        <v>354</v>
+      </c>
+      <c r="B35" s="98">
+        <v>723</v>
+      </c>
+      <c r="C35" s="95">
+        <v>41.8</v>
+      </c>
+      <c r="D35" s="94">
+        <v>2.17</v>
+      </c>
+      <c r="E35" s="98">
+        <v>57300</v>
+      </c>
+      <c r="F35" s="98">
+        <v>3270</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" s="97" t="s">
+        <v>353</v>
+      </c>
+      <c r="B36" s="98">
+        <v>652</v>
+      </c>
+      <c r="C36" s="95">
+        <v>41.1</v>
+      </c>
+      <c r="D36" s="94">
+        <v>1.97</v>
+      </c>
+      <c r="E36" s="98">
+        <v>50600</v>
+      </c>
+      <c r="F36" s="98">
+        <v>2910</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="97" t="s">
+        <v>352</v>
+      </c>
+      <c r="B37" s="98">
+        <v>529</v>
+      </c>
+      <c r="C37" s="95">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="D37" s="94">
+        <v>1.61</v>
+      </c>
+      <c r="E37" s="98">
+        <v>39600</v>
+      </c>
+      <c r="F37" s="98">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" s="97" t="s">
+        <v>351</v>
+      </c>
+      <c r="B38" s="98">
+        <v>487</v>
+      </c>
+      <c r="C38" s="95">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="D38" s="94">
+        <v>1.5</v>
+      </c>
+      <c r="E38" s="98">
+        <v>36000</v>
+      </c>
+      <c r="F38" s="98">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="B39" s="98">
+        <v>441</v>
+      </c>
+      <c r="C39" s="95">
+        <v>38.9</v>
+      </c>
+      <c r="D39" s="94">
+        <v>1.36</v>
+      </c>
+      <c r="E39" s="98">
+        <v>32100</v>
+      </c>
+      <c r="F39" s="98">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" s="97" t="s">
+        <v>349</v>
+      </c>
+      <c r="B40" s="98">
+        <v>395</v>
+      </c>
+      <c r="C40" s="95">
+        <v>38.4</v>
+      </c>
+      <c r="D40" s="94">
+        <v>1.22</v>
+      </c>
+      <c r="E40" s="98">
+        <v>28500</v>
+      </c>
+      <c r="F40" s="98">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" s="97" t="s">
+        <v>348</v>
+      </c>
+      <c r="B41" s="98">
+        <v>361</v>
+      </c>
+      <c r="C41" s="95">
+        <v>38</v>
+      </c>
+      <c r="D41" s="94">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="E41" s="98">
+        <v>25700</v>
+      </c>
+      <c r="F41" s="98">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" s="97" t="s">
+        <v>347</v>
+      </c>
+      <c r="B42" s="98">
+        <v>330</v>
+      </c>
+      <c r="C42" s="95">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="D42" s="94">
+        <v>1.02</v>
+      </c>
+      <c r="E42" s="98">
+        <v>23300</v>
+      </c>
+      <c r="F42" s="98">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" s="97" t="s">
+        <v>346</v>
+      </c>
+      <c r="B43" s="98">
+        <v>302</v>
+      </c>
+      <c r="C43" s="95">
+        <v>37.299999999999997</v>
+      </c>
+      <c r="D43" s="96">
+        <v>0.94499999999999995</v>
+      </c>
+      <c r="E43" s="98">
+        <v>21100</v>
+      </c>
+      <c r="F43" s="98">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" s="97" t="s">
+        <v>345</v>
+      </c>
+      <c r="B44" s="98">
+        <v>282</v>
+      </c>
+      <c r="C44" s="95">
+        <v>37.1</v>
+      </c>
+      <c r="D44" s="96">
+        <v>0.88500000000000001</v>
+      </c>
+      <c r="E44" s="98">
+        <v>19600</v>
+      </c>
+      <c r="F44" s="98">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" s="97" t="s">
+        <v>344</v>
+      </c>
+      <c r="B45" s="98">
+        <v>262</v>
+      </c>
+      <c r="C45" s="95">
+        <v>36.9</v>
+      </c>
+      <c r="D45" s="96">
+        <v>0.84</v>
+      </c>
+      <c r="E45" s="98">
+        <v>17900</v>
+      </c>
+      <c r="F45" s="98">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" s="97" t="s">
+        <v>343</v>
+      </c>
+      <c r="B46" s="98">
+        <v>247</v>
+      </c>
+      <c r="C46" s="95">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="D46" s="96">
+        <v>0.8</v>
+      </c>
+      <c r="E46" s="98">
+        <v>16700</v>
+      </c>
+      <c r="F46" s="98">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" s="97" t="s">
+        <v>342</v>
+      </c>
+      <c r="B47" s="98">
+        <v>231</v>
+      </c>
+      <c r="C47" s="95">
+        <v>36.5</v>
+      </c>
+      <c r="D47" s="96">
+        <v>0.76</v>
+      </c>
+      <c r="E47" s="98">
+        <v>15600</v>
+      </c>
+      <c r="F47" s="98">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" s="97" t="s">
+        <v>341</v>
+      </c>
+      <c r="B48" s="98">
+        <v>387</v>
+      </c>
+      <c r="C48" s="95">
+        <v>39.1</v>
+      </c>
+      <c r="D48" s="94">
+        <v>1.42</v>
+      </c>
+      <c r="E48" s="98">
+        <v>26500</v>
+      </c>
+      <c r="F48" s="98">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" s="97" t="s">
+        <v>340</v>
+      </c>
+      <c r="B49" s="98">
+        <v>350</v>
+      </c>
+      <c r="C49" s="95">
+        <v>38.6</v>
+      </c>
+      <c r="D49" s="94">
+        <v>1.3</v>
+      </c>
+      <c r="E49" s="98">
+        <v>23600</v>
+      </c>
+      <c r="F49" s="98">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" s="97" t="s">
+        <v>339</v>
+      </c>
+      <c r="B50" s="98">
+        <v>318</v>
+      </c>
+      <c r="C50" s="95">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="D50" s="94">
+        <v>1.18</v>
+      </c>
+      <c r="E50" s="98">
+        <v>21200</v>
+      </c>
+      <c r="F50" s="98">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" s="97" t="s">
+        <v>338</v>
+      </c>
+      <c r="B51" s="98">
+        <v>286</v>
+      </c>
+      <c r="C51" s="95">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="D51" s="94">
+        <v>1.06</v>
+      </c>
+      <c r="E51" s="98">
+        <v>18900</v>
+      </c>
+      <c r="F51" s="98">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52" s="97" t="s">
+        <v>337</v>
+      </c>
+      <c r="B52" s="98">
+        <v>256</v>
+      </c>
+      <c r="C52" s="95">
+        <v>37.4</v>
+      </c>
+      <c r="D52" s="96">
+        <v>0.96</v>
+      </c>
+      <c r="E52" s="98">
+        <v>16800</v>
+      </c>
+      <c r="F52" s="98">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53" s="97" t="s">
+        <v>336</v>
+      </c>
+      <c r="B53" s="98">
+        <v>232</v>
+      </c>
+      <c r="C53" s="95">
+        <v>37.1</v>
+      </c>
+      <c r="D53" s="96">
+        <v>0.87</v>
+      </c>
+      <c r="E53" s="98">
+        <v>15000</v>
+      </c>
+      <c r="F53" s="98">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54" s="97" t="s">
+        <v>335</v>
+      </c>
+      <c r="B54" s="98">
+        <v>210</v>
+      </c>
+      <c r="C54" s="95">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="D54" s="96">
+        <v>0.83</v>
+      </c>
+      <c r="E54" s="98">
+        <v>13200</v>
+      </c>
+      <c r="F54" s="98">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" s="97" t="s">
+        <v>334</v>
+      </c>
+      <c r="B55" s="98">
+        <v>194</v>
+      </c>
+      <c r="C55" s="95">
+        <v>36.5</v>
+      </c>
+      <c r="D55" s="96">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="E55" s="98">
+        <v>12100</v>
+      </c>
+      <c r="F55" s="98">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" s="97" t="s">
+        <v>333</v>
+      </c>
+      <c r="B56" s="98">
+        <v>182</v>
+      </c>
+      <c r="C56" s="95">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="D56" s="96">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="E56" s="98">
+        <v>11300</v>
+      </c>
+      <c r="F56" s="98">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A57" s="97" t="s">
+        <v>332</v>
+      </c>
+      <c r="B57" s="98">
+        <v>170</v>
+      </c>
+      <c r="C57" s="95">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="D57" s="96">
+        <v>0.68</v>
+      </c>
+      <c r="E57" s="98">
+        <v>10500</v>
+      </c>
+      <c r="F57" s="98">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" s="97" t="s">
+        <v>331</v>
+      </c>
+      <c r="B58" s="98">
+        <v>160</v>
+      </c>
+      <c r="C58" s="95">
+        <v>36</v>
+      </c>
+      <c r="D58" s="96">
+        <v>0.65</v>
+      </c>
+      <c r="E58" s="98">
+        <v>9760</v>
+      </c>
+      <c r="F58" s="98">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" s="97" t="s">
+        <v>330</v>
+      </c>
+      <c r="B59" s="98">
+        <v>150</v>
+      </c>
+      <c r="C59" s="95">
+        <v>35.9</v>
+      </c>
+      <c r="D59" s="96">
+        <v>0.625</v>
+      </c>
+      <c r="E59" s="98">
+        <v>9040</v>
+      </c>
+      <c r="F59" s="98">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A60" s="97" t="s">
+        <v>329</v>
+      </c>
+      <c r="B60" s="98">
+        <v>135</v>
+      </c>
+      <c r="C60" s="95">
+        <v>35.6</v>
+      </c>
+      <c r="D60" s="96">
+        <v>0.6</v>
+      </c>
+      <c r="E60" s="98">
+        <v>7800</v>
+      </c>
+      <c r="F60" s="98">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A61" s="97" t="s">
+        <v>328</v>
+      </c>
+      <c r="B61" s="98">
+        <v>387</v>
+      </c>
+      <c r="C61" s="95">
+        <v>36</v>
+      </c>
+      <c r="D61" s="94">
+        <v>1.26</v>
+      </c>
+      <c r="E61" s="98">
+        <v>24300</v>
+      </c>
+      <c r="F61" s="98">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A62" s="97" t="s">
+        <v>327</v>
+      </c>
+      <c r="B62" s="98">
+        <v>354</v>
+      </c>
+      <c r="C62" s="95">
+        <v>35.6</v>
+      </c>
+      <c r="D62" s="94">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="E62" s="98">
+        <v>22000</v>
+      </c>
+      <c r="F62" s="98">
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A63" s="97" t="s">
+        <v>326</v>
+      </c>
+      <c r="B63" s="98">
+        <v>318</v>
+      </c>
+      <c r="C63" s="95">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="D63" s="94">
+        <v>1.04</v>
+      </c>
+      <c r="E63" s="98">
+        <v>19500</v>
+      </c>
+      <c r="F63" s="98">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A64" s="97" t="s">
+        <v>325</v>
+      </c>
+      <c r="B64" s="98">
+        <v>291</v>
+      </c>
+      <c r="C64" s="95">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="D64" s="96">
+        <v>0.96</v>
+      </c>
+      <c r="E64" s="98">
+        <v>17700</v>
+      </c>
+      <c r="F64" s="98">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A65" s="97" t="s">
+        <v>324</v>
+      </c>
+      <c r="B65" s="98">
+        <v>263</v>
+      </c>
+      <c r="C65" s="95">
+        <v>34.5</v>
+      </c>
+      <c r="D65" s="96">
+        <v>0.87</v>
+      </c>
+      <c r="E65" s="98">
+        <v>15900</v>
+      </c>
+      <c r="F65" s="98">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66" s="97" t="s">
+        <v>323</v>
+      </c>
+      <c r="B66" s="98">
+        <v>241</v>
+      </c>
+      <c r="C66" s="95">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="D66" s="96">
+        <v>0.83</v>
+      </c>
+      <c r="E66" s="98">
+        <v>14200</v>
+      </c>
+      <c r="F66" s="98">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A67" s="97" t="s">
+        <v>322</v>
+      </c>
+      <c r="B67" s="98">
+        <v>221</v>
+      </c>
+      <c r="C67" s="95">
+        <v>33.9</v>
+      </c>
+      <c r="D67" s="96">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="E67" s="98">
+        <v>12900</v>
+      </c>
+      <c r="F67" s="98">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A68" s="97" t="s">
+        <v>321</v>
+      </c>
+      <c r="B68" s="98">
+        <v>201</v>
+      </c>
+      <c r="C68" s="95">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="D68" s="96">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="E68" s="98">
+        <v>11600</v>
+      </c>
+      <c r="F68" s="98">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="97" t="s">
+        <v>320</v>
+      </c>
+      <c r="B69" s="98">
+        <v>169</v>
+      </c>
+      <c r="C69" s="95">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="D69" s="96">
+        <v>0.67</v>
+      </c>
+      <c r="E69" s="98">
+        <v>9290</v>
+      </c>
+      <c r="F69" s="98">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A70" s="97" t="s">
+        <v>319</v>
+      </c>
+      <c r="B70" s="98">
+        <v>152</v>
+      </c>
+      <c r="C70" s="95">
+        <v>33.5</v>
+      </c>
+      <c r="D70" s="96">
+        <v>0.63500000000000001</v>
+      </c>
+      <c r="E70" s="98">
+        <v>8160</v>
+      </c>
+      <c r="F70" s="98">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" s="97" t="s">
+        <v>318</v>
+      </c>
+      <c r="B71" s="98">
+        <v>141</v>
+      </c>
+      <c r="C71" s="95">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="D71" s="96">
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="E71" s="98">
+        <v>7450</v>
+      </c>
+      <c r="F71" s="98">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72" s="97" t="s">
+        <v>317</v>
+      </c>
+      <c r="B72" s="98">
+        <v>130</v>
+      </c>
+      <c r="C72" s="95">
+        <v>33.1</v>
+      </c>
+      <c r="D72" s="96">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="E72" s="98">
+        <v>6710</v>
+      </c>
+      <c r="F72" s="98">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A73" s="97" t="s">
+        <v>316</v>
+      </c>
+      <c r="B73" s="98">
+        <v>118</v>
+      </c>
+      <c r="C73" s="95">
+        <v>32.9</v>
+      </c>
+      <c r="D73" s="96">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E73" s="98">
+        <v>5900</v>
+      </c>
+      <c r="F73" s="98">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A74" s="97" t="s">
+        <v>315</v>
+      </c>
+      <c r="B74" s="98">
+        <v>391</v>
+      </c>
+      <c r="C74" s="95">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="D74" s="94">
+        <v>1.36</v>
+      </c>
+      <c r="E74" s="98">
+        <v>20700</v>
+      </c>
+      <c r="F74" s="98">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A75" s="97" t="s">
+        <v>314</v>
+      </c>
+      <c r="B75" s="98">
+        <v>357</v>
+      </c>
+      <c r="C75" s="95">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="D75" s="94">
+        <v>1.24</v>
+      </c>
+      <c r="E75" s="98">
+        <v>18700</v>
+      </c>
+      <c r="F75" s="98">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A76" s="97" t="s">
+        <v>313</v>
+      </c>
+      <c r="B76" s="98">
+        <v>326</v>
+      </c>
+      <c r="C76" s="95">
+        <v>32.4</v>
+      </c>
+      <c r="D76" s="94">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="E76" s="98">
+        <v>16800</v>
+      </c>
+      <c r="F76" s="98">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A77" s="97" t="s">
+        <v>312</v>
+      </c>
+      <c r="B77" s="98">
+        <v>292</v>
+      </c>
+      <c r="C77" s="95">
+        <v>32</v>
+      </c>
+      <c r="D77" s="94">
+        <v>1.02</v>
+      </c>
+      <c r="E77" s="98">
+        <v>14900</v>
+      </c>
+      <c r="F77" s="98">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A78" s="97" t="s">
+        <v>311</v>
+      </c>
+      <c r="B78" s="98">
+        <v>261</v>
+      </c>
+      <c r="C78" s="95">
+        <v>31.6</v>
+      </c>
+      <c r="D78" s="96">
+        <v>0.93</v>
+      </c>
+      <c r="E78" s="98">
+        <v>13100</v>
+      </c>
+      <c r="F78" s="98">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A79" s="97" t="s">
+        <v>310</v>
+      </c>
+      <c r="B79" s="98">
+        <v>235</v>
+      </c>
+      <c r="C79" s="95">
+        <v>31.3</v>
+      </c>
+      <c r="D79" s="96">
+        <v>0.83</v>
+      </c>
+      <c r="E79" s="98">
+        <v>11700</v>
+      </c>
+      <c r="F79" s="98">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80" s="97" t="s">
+        <v>309</v>
+      </c>
+      <c r="B80" s="98">
+        <v>211</v>
+      </c>
+      <c r="C80" s="95">
+        <v>30.9</v>
+      </c>
+      <c r="D80" s="96">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="E80" s="98">
+        <v>10300</v>
+      </c>
+      <c r="F80" s="98">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A81" s="97" t="s">
+        <v>308</v>
+      </c>
+      <c r="B81" s="98">
+        <v>191</v>
+      </c>
+      <c r="C81" s="95">
+        <v>30.7</v>
+      </c>
+      <c r="D81" s="96">
+        <v>0.71</v>
+      </c>
+      <c r="E81" s="98">
+        <v>9200</v>
+      </c>
+      <c r="F81" s="98">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A82" s="97" t="s">
+        <v>307</v>
+      </c>
+      <c r="B82" s="98">
+        <v>173</v>
+      </c>
+      <c r="C82" s="95">
+        <v>30.4</v>
+      </c>
+      <c r="D82" s="96">
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="E82" s="98">
+        <v>8230</v>
+      </c>
+      <c r="F82" s="98">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A83" s="97" t="s">
+        <v>306</v>
+      </c>
+      <c r="B83" s="98">
+        <v>148</v>
+      </c>
+      <c r="C83" s="95">
+        <v>30.7</v>
+      </c>
+      <c r="D83" s="96">
+        <v>0.65</v>
+      </c>
+      <c r="E83" s="98">
+        <v>6680</v>
+      </c>
+      <c r="F83" s="98">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A84" s="97" t="s">
+        <v>305</v>
+      </c>
+      <c r="B84" s="98">
+        <v>132</v>
+      </c>
+      <c r="C84" s="95">
+        <v>30.3</v>
+      </c>
+      <c r="D84" s="96">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="E84" s="98">
+        <v>5770</v>
+      </c>
+      <c r="F84" s="98">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A85" s="97" t="s">
+        <v>304</v>
+      </c>
+      <c r="B85" s="98">
+        <v>124</v>
+      </c>
+      <c r="C85" s="95">
+        <v>30.2</v>
+      </c>
+      <c r="D85" s="96">
+        <v>0.58499999999999996</v>
+      </c>
+      <c r="E85" s="98">
+        <v>5360</v>
+      </c>
+      <c r="F85" s="98">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A86" s="97" t="s">
+        <v>303</v>
+      </c>
+      <c r="B86" s="98">
+        <v>116</v>
+      </c>
+      <c r="C86" s="95">
+        <v>30</v>
+      </c>
+      <c r="D86" s="96">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="E86" s="98">
+        <v>4930</v>
+      </c>
+      <c r="F86" s="98">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A87" s="97" t="s">
+        <v>302</v>
+      </c>
+      <c r="B87" s="98">
+        <v>108</v>
+      </c>
+      <c r="C87" s="95">
+        <v>29.8</v>
+      </c>
+      <c r="D87" s="96">
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="E87" s="98">
+        <v>4470</v>
+      </c>
+      <c r="F87" s="98">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A88" s="97" t="s">
+        <v>301</v>
+      </c>
+      <c r="B88" s="95">
+        <v>99</v>
+      </c>
+      <c r="C88" s="95">
+        <v>29.7</v>
+      </c>
+      <c r="D88" s="96">
+        <v>0.52</v>
+      </c>
+      <c r="E88" s="98">
+        <v>3990</v>
+      </c>
+      <c r="F88" s="98">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A89" s="97" t="s">
+        <v>300</v>
+      </c>
+      <c r="B89" s="95">
+        <v>90</v>
+      </c>
+      <c r="C89" s="95">
+        <v>29.5</v>
+      </c>
+      <c r="D89" s="96">
+        <v>0.47</v>
+      </c>
+      <c r="E89" s="98">
+        <v>3610</v>
+      </c>
+      <c r="F89" s="98">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A90" s="97" t="s">
+        <v>299</v>
+      </c>
+      <c r="B90" s="98">
+        <v>539</v>
+      </c>
+      <c r="C90" s="95">
+        <v>32.5</v>
+      </c>
+      <c r="D90" s="94">
+        <v>1.97</v>
+      </c>
+      <c r="E90" s="98">
+        <v>25600</v>
+      </c>
+      <c r="F90" s="98">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A91" s="97" t="s">
+        <v>298</v>
+      </c>
+      <c r="B91" s="98">
+        <v>368</v>
+      </c>
+      <c r="C91" s="95">
+        <v>30.4</v>
+      </c>
+      <c r="D91" s="94">
+        <v>1.38</v>
+      </c>
+      <c r="E91" s="98">
+        <v>16200</v>
+      </c>
+      <c r="F91" s="98">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A92" s="97" t="s">
+        <v>297</v>
+      </c>
+      <c r="B92" s="98">
+        <v>336</v>
+      </c>
+      <c r="C92" s="95">
+        <v>30</v>
+      </c>
+      <c r="D92" s="94">
+        <v>1.26</v>
+      </c>
+      <c r="E92" s="98">
+        <v>14600</v>
+      </c>
+      <c r="F92" s="98">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A93" s="97" t="s">
+        <v>296</v>
+      </c>
+      <c r="B93" s="98">
+        <v>307</v>
+      </c>
+      <c r="C93" s="95">
+        <v>29.6</v>
+      </c>
+      <c r="D93" s="94">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="E93" s="98">
+        <v>13100</v>
+      </c>
+      <c r="F93" s="98">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A94" s="97" t="s">
+        <v>295</v>
+      </c>
+      <c r="B94" s="98">
+        <v>281</v>
+      </c>
+      <c r="C94" s="95">
+        <v>29.3</v>
+      </c>
+      <c r="D94" s="94">
+        <v>1.06</v>
+      </c>
+      <c r="E94" s="98">
+        <v>11900</v>
+      </c>
+      <c r="F94" s="98">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A95" s="97" t="s">
+        <v>294</v>
+      </c>
+      <c r="B95" s="98">
+        <v>258</v>
+      </c>
+      <c r="C95" s="95">
+        <v>29</v>
+      </c>
+      <c r="D95" s="96">
+        <v>0.98</v>
+      </c>
+      <c r="E95" s="98">
+        <v>10800</v>
+      </c>
+      <c r="F95" s="98">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A96" s="97" t="s">
+        <v>293</v>
+      </c>
+      <c r="B96" s="98">
+        <v>235</v>
+      </c>
+      <c r="C96" s="95">
+        <v>28.7</v>
+      </c>
+      <c r="D96" s="96">
+        <v>0.91</v>
+      </c>
+      <c r="E96" s="98">
+        <v>9700</v>
+      </c>
+      <c r="F96" s="98">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A97" s="97" t="s">
+        <v>292</v>
+      </c>
+      <c r="B97" s="98">
+        <v>217</v>
+      </c>
+      <c r="C97" s="95">
+        <v>28.4</v>
+      </c>
+      <c r="D97" s="96">
+        <v>0.83</v>
+      </c>
+      <c r="E97" s="98">
+        <v>8910</v>
+      </c>
+      <c r="F97" s="98">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A98" s="97" t="s">
+        <v>291</v>
+      </c>
+      <c r="B98" s="98">
+        <v>194</v>
+      </c>
+      <c r="C98" s="95">
+        <v>28.1</v>
+      </c>
+      <c r="D98" s="96">
+        <v>0.75</v>
+      </c>
+      <c r="E98" s="98">
+        <v>7860</v>
+      </c>
+      <c r="F98" s="98">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A99" s="97" t="s">
+        <v>290</v>
+      </c>
+      <c r="B99" s="98">
+        <v>178</v>
+      </c>
+      <c r="C99" s="95">
+        <v>27.8</v>
+      </c>
+      <c r="D99" s="96">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="E99" s="98">
+        <v>7020</v>
+      </c>
+      <c r="F99" s="98">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A100" s="97" t="s">
+        <v>289</v>
+      </c>
+      <c r="B100" s="98">
+        <v>161</v>
+      </c>
+      <c r="C100" s="95">
+        <v>27.6</v>
+      </c>
+      <c r="D100" s="96">
+        <v>0.66</v>
+      </c>
+      <c r="E100" s="98">
+        <v>6310</v>
+      </c>
+      <c r="F100" s="98">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A101" s="97" t="s">
+        <v>288</v>
+      </c>
+      <c r="B101" s="98">
+        <v>146</v>
+      </c>
+      <c r="C101" s="95">
+        <v>27.4</v>
+      </c>
+      <c r="D101" s="96">
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="E101" s="98">
+        <v>5660</v>
+      </c>
+      <c r="F101" s="98">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A102" s="97" t="s">
+        <v>287</v>
+      </c>
+      <c r="B102" s="98">
+        <v>129</v>
+      </c>
+      <c r="C102" s="95">
+        <v>27.6</v>
+      </c>
+      <c r="D102" s="96">
+        <v>0.61</v>
+      </c>
+      <c r="E102" s="98">
+        <v>4760</v>
+      </c>
+      <c r="F102" s="98">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A103" s="97" t="s">
+        <v>286</v>
+      </c>
+      <c r="B103" s="98">
+        <v>114</v>
+      </c>
+      <c r="C103" s="95">
+        <v>27.3</v>
+      </c>
+      <c r="D103" s="96">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="E103" s="98">
+        <v>4080</v>
+      </c>
+      <c r="F103" s="98">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A104" s="97" t="s">
+        <v>285</v>
+      </c>
+      <c r="B104" s="98">
+        <v>102</v>
+      </c>
+      <c r="C104" s="95">
+        <v>27.1</v>
+      </c>
+      <c r="D104" s="96">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="E104" s="98">
+        <v>3620</v>
+      </c>
+      <c r="F104" s="98">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A105" s="97" t="s">
+        <v>284</v>
+      </c>
+      <c r="B105" s="95">
+        <v>94</v>
+      </c>
+      <c r="C105" s="95">
+        <v>26.9</v>
+      </c>
+      <c r="D105" s="96">
+        <v>0.49</v>
+      </c>
+      <c r="E105" s="98">
+        <v>3270</v>
+      </c>
+      <c r="F105" s="98">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A106" s="97" t="s">
+        <v>283</v>
+      </c>
+      <c r="B106" s="95">
+        <v>84</v>
+      </c>
+      <c r="C106" s="95">
+        <v>26.7</v>
+      </c>
+      <c r="D106" s="96">
+        <v>0.46</v>
+      </c>
+      <c r="E106" s="98">
+        <v>2850</v>
+      </c>
+      <c r="F106" s="98">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A107" s="97" t="s">
+        <v>282</v>
+      </c>
+      <c r="B107" s="98">
+        <v>370</v>
+      </c>
+      <c r="C107" s="95">
+        <v>28</v>
+      </c>
+      <c r="D107" s="94">
+        <v>1.52</v>
+      </c>
+      <c r="E107" s="98">
+        <v>13400</v>
+      </c>
+      <c r="F107" s="98">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A108" s="97" t="s">
+        <v>281</v>
+      </c>
+      <c r="B108" s="98">
+        <v>335</v>
+      </c>
+      <c r="C108" s="95">
+        <v>27.5</v>
+      </c>
+      <c r="D108" s="94">
+        <v>1.38</v>
+      </c>
+      <c r="E108" s="98">
+        <v>11900</v>
+      </c>
+      <c r="F108" s="98">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A109" s="97" t="s">
+        <v>280</v>
+      </c>
+      <c r="B109" s="98">
+        <v>306</v>
+      </c>
+      <c r="C109" s="95">
+        <v>27.1</v>
+      </c>
+      <c r="D109" s="94">
+        <v>1.26</v>
+      </c>
+      <c r="E109" s="98">
+        <v>10700</v>
+      </c>
+      <c r="F109" s="98">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A110" s="97" t="s">
+        <v>279</v>
+      </c>
+      <c r="B110" s="98">
+        <v>279</v>
+      </c>
+      <c r="C110" s="95">
+        <v>26.7</v>
+      </c>
+      <c r="D110" s="94">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="E110" s="98">
+        <v>9600</v>
+      </c>
+      <c r="F110" s="98">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A111" s="97" t="s">
+        <v>278</v>
+      </c>
+      <c r="B111" s="98">
+        <v>250</v>
+      </c>
+      <c r="C111" s="95">
+        <v>26.3</v>
+      </c>
+      <c r="D111" s="94">
+        <v>1.04</v>
+      </c>
+      <c r="E111" s="98">
+        <v>8490</v>
+      </c>
+      <c r="F111" s="98">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A112" s="97" t="s">
+        <v>277</v>
+      </c>
+      <c r="B112" s="98">
+        <v>229</v>
+      </c>
+      <c r="C112" s="95">
+        <v>26</v>
+      </c>
+      <c r="D112" s="96">
+        <v>0.96</v>
+      </c>
+      <c r="E112" s="98">
+        <v>7650</v>
+      </c>
+      <c r="F112" s="98">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A113" s="97" t="s">
+        <v>276</v>
+      </c>
+      <c r="B113" s="98">
+        <v>207</v>
+      </c>
+      <c r="C113" s="95">
+        <v>25.7</v>
+      </c>
+      <c r="D113" s="96">
+        <v>0.87</v>
+      </c>
+      <c r="E113" s="98">
+        <v>6820</v>
+      </c>
+      <c r="F113" s="98">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A114" s="97" t="s">
+        <v>275</v>
+      </c>
+      <c r="B114" s="98">
+        <v>192</v>
+      </c>
+      <c r="C114" s="95">
+        <v>25.5</v>
+      </c>
+      <c r="D114" s="96">
+        <v>0.81</v>
+      </c>
+      <c r="E114" s="98">
+        <v>6260</v>
+      </c>
+      <c r="F114" s="98">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A115" s="97" t="s">
+        <v>274</v>
+      </c>
+      <c r="B115" s="98">
+        <v>176</v>
+      </c>
+      <c r="C115" s="95">
+        <v>25.2</v>
+      </c>
+      <c r="D115" s="96">
+        <v>0.75</v>
+      </c>
+      <c r="E115" s="98">
+        <v>5680</v>
+      </c>
+      <c r="F115" s="98">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A116" s="97" t="s">
+        <v>273</v>
+      </c>
+      <c r="B116" s="98">
+        <v>162</v>
+      </c>
+      <c r="C116" s="95">
+        <v>25</v>
+      </c>
+      <c r="D116" s="96">
+        <v>0.70499999999999996</v>
+      </c>
+      <c r="E116" s="98">
+        <v>5170</v>
+      </c>
+      <c r="F116" s="98">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A117" s="97" t="s">
+        <v>272</v>
+      </c>
+      <c r="B117" s="98">
+        <v>146</v>
+      </c>
+      <c r="C117" s="95">
+        <v>24.7</v>
+      </c>
+      <c r="D117" s="96">
+        <v>0.65</v>
+      </c>
+      <c r="E117" s="98">
+        <v>4580</v>
+      </c>
+      <c r="F117" s="98">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A118" s="97" t="s">
+        <v>271</v>
+      </c>
+      <c r="B118" s="98">
+        <v>131</v>
+      </c>
+      <c r="C118" s="95">
+        <v>24.5</v>
+      </c>
+      <c r="D118" s="96">
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="E118" s="98">
+        <v>4020</v>
+      </c>
+      <c r="F118" s="98">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A119" s="97" t="s">
+        <v>270</v>
+      </c>
+      <c r="B119" s="98">
+        <v>117</v>
+      </c>
+      <c r="C119" s="95">
+        <v>24.3</v>
+      </c>
+      <c r="D119" s="96">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E119" s="98">
+        <v>3540</v>
+      </c>
+      <c r="F119" s="98">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A120" s="97" t="s">
+        <v>269</v>
+      </c>
+      <c r="B120" s="98">
+        <v>104</v>
+      </c>
+      <c r="C120" s="95">
+        <v>24.1</v>
+      </c>
+      <c r="D120" s="96">
+        <v>0.5</v>
+      </c>
+      <c r="E120" s="98">
+        <v>3100</v>
+      </c>
+      <c r="F120" s="98">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A121" s="97" t="s">
+        <v>268</v>
+      </c>
+      <c r="B121" s="98">
+        <v>103</v>
+      </c>
+      <c r="C121" s="95">
+        <v>24.5</v>
+      </c>
+      <c r="D121" s="96">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E121" s="98">
+        <v>3000</v>
+      </c>
+      <c r="F121" s="98">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A122" s="97" t="s">
+        <v>267</v>
+      </c>
+      <c r="B122" s="95">
+        <v>94</v>
+      </c>
+      <c r="C122" s="95">
+        <v>24.3</v>
+      </c>
+      <c r="D122" s="96">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="E122" s="98">
+        <v>2700</v>
+      </c>
+      <c r="F122" s="98">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A123" s="97" t="s">
+        <v>266</v>
+      </c>
+      <c r="B123" s="95">
+        <v>84</v>
+      </c>
+      <c r="C123" s="95">
+        <v>24.1</v>
+      </c>
+      <c r="D123" s="96">
+        <v>0.47</v>
+      </c>
+      <c r="E123" s="98">
+        <v>2370</v>
+      </c>
+      <c r="F123" s="98">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A124" s="97" t="s">
+        <v>265</v>
+      </c>
+      <c r="B124" s="95">
+        <v>76</v>
+      </c>
+      <c r="C124" s="95">
+        <v>23.9</v>
+      </c>
+      <c r="D124" s="96">
+        <v>0.44</v>
+      </c>
+      <c r="E124" s="98">
+        <v>2100</v>
+      </c>
+      <c r="F124" s="98">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A125" s="97" t="s">
+        <v>264</v>
+      </c>
+      <c r="B125" s="95">
+        <v>68</v>
+      </c>
+      <c r="C125" s="95">
+        <v>23.7</v>
+      </c>
+      <c r="D125" s="96">
+        <v>0.41499999999999998</v>
+      </c>
+      <c r="E125" s="98">
+        <v>1830</v>
+      </c>
+      <c r="F125" s="98">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A126" s="97" t="s">
+        <v>263</v>
+      </c>
+      <c r="B126" s="95">
+        <v>62</v>
+      </c>
+      <c r="C126" s="95">
+        <v>23.7</v>
+      </c>
+      <c r="D126" s="96">
+        <v>0.43</v>
+      </c>
+      <c r="E126" s="98">
+        <v>1550</v>
+      </c>
+      <c r="F126" s="98">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A127" s="97" t="s">
+        <v>262</v>
+      </c>
+      <c r="B127" s="95">
+        <v>55</v>
+      </c>
+      <c r="C127" s="95">
+        <v>23.6</v>
+      </c>
+      <c r="D127" s="96">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="E127" s="98">
+        <v>1350</v>
+      </c>
+      <c r="F127" s="98">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A128" s="97" t="s">
+        <v>261</v>
+      </c>
+      <c r="B128" s="98">
+        <v>275</v>
+      </c>
+      <c r="C128" s="95">
+        <v>24.1</v>
+      </c>
+      <c r="D128" s="94">
+        <v>1.22</v>
+      </c>
+      <c r="E128" s="98">
+        <v>7690</v>
+      </c>
+      <c r="F128" s="98">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A129" s="97" t="s">
+        <v>260</v>
+      </c>
+      <c r="B129" s="98">
+        <v>248</v>
+      </c>
+      <c r="C129" s="95">
+        <v>23.7</v>
+      </c>
+      <c r="D129" s="94">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E129" s="98">
+        <v>6830</v>
+      </c>
+      <c r="F129" s="98">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A130" s="97" t="s">
+        <v>259</v>
+      </c>
+      <c r="B130" s="98">
+        <v>223</v>
+      </c>
+      <c r="C130" s="95">
+        <v>23.4</v>
+      </c>
+      <c r="D130" s="94">
+        <v>1</v>
+      </c>
+      <c r="E130" s="98">
+        <v>6080</v>
+      </c>
+      <c r="F130" s="98">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A131" s="97" t="s">
+        <v>258</v>
+      </c>
+      <c r="B131" s="98">
+        <v>201</v>
+      </c>
+      <c r="C131" s="95">
+        <v>23</v>
+      </c>
+      <c r="D131" s="96">
+        <v>0.91</v>
+      </c>
+      <c r="E131" s="98">
+        <v>5310</v>
+      </c>
+      <c r="F131" s="98">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A132" s="97" t="s">
+        <v>257</v>
+      </c>
+      <c r="B132" s="98">
+        <v>182</v>
+      </c>
+      <c r="C132" s="95">
+        <v>22.7</v>
+      </c>
+      <c r="D132" s="96">
+        <v>0.83</v>
+      </c>
+      <c r="E132" s="98">
+        <v>4730</v>
+      </c>
+      <c r="F132" s="98">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A133" s="97" t="s">
+        <v>256</v>
+      </c>
+      <c r="B133" s="98">
+        <v>166</v>
+      </c>
+      <c r="C133" s="95">
+        <v>22.5</v>
+      </c>
+      <c r="D133" s="96">
+        <v>0.75</v>
+      </c>
+      <c r="E133" s="98">
+        <v>4280</v>
+      </c>
+      <c r="F133" s="98">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A134" s="97" t="s">
+        <v>255</v>
+      </c>
+      <c r="B134" s="98">
+        <v>147</v>
+      </c>
+      <c r="C134" s="95">
+        <v>22.1</v>
+      </c>
+      <c r="D134" s="96">
+        <v>0.72</v>
+      </c>
+      <c r="E134" s="98">
+        <v>3630</v>
+      </c>
+      <c r="F134" s="98">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A135" s="97" t="s">
+        <v>254</v>
+      </c>
+      <c r="B135" s="98">
+        <v>132</v>
+      </c>
+      <c r="C135" s="95">
+        <v>21.8</v>
+      </c>
+      <c r="D135" s="96">
+        <v>0.65</v>
+      </c>
+      <c r="E135" s="98">
+        <v>3220</v>
+      </c>
+      <c r="F135" s="98">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A136" s="97" t="s">
+        <v>253</v>
+      </c>
+      <c r="B136" s="98">
+        <v>122</v>
+      </c>
+      <c r="C136" s="95">
+        <v>21.7</v>
+      </c>
+      <c r="D136" s="96">
+        <v>0.6</v>
+      </c>
+      <c r="E136" s="98">
+        <v>2960</v>
+      </c>
+      <c r="F136" s="98">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A137" s="97" t="s">
+        <v>252</v>
+      </c>
+      <c r="B137" s="98">
+        <v>111</v>
+      </c>
+      <c r="C137" s="95">
+        <v>21.5</v>
+      </c>
+      <c r="D137" s="96">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E137" s="98">
+        <v>2670</v>
+      </c>
+      <c r="F137" s="98">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A138" s="97" t="s">
+        <v>251</v>
+      </c>
+      <c r="B138" s="98">
+        <v>101</v>
+      </c>
+      <c r="C138" s="95">
+        <v>21.4</v>
+      </c>
+      <c r="D138" s="96">
+        <v>0.5</v>
+      </c>
+      <c r="E138" s="98">
+        <v>2420</v>
+      </c>
+      <c r="F138" s="98">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A139" s="97" t="s">
+        <v>250</v>
+      </c>
+      <c r="B139" s="95">
+        <v>93</v>
+      </c>
+      <c r="C139" s="95">
+        <v>21.6</v>
+      </c>
+      <c r="D139" s="96">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="E139" s="98">
+        <v>2070</v>
+      </c>
+      <c r="F139" s="98">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A140" s="97" t="s">
+        <v>249</v>
+      </c>
+      <c r="B140" s="95">
+        <v>83</v>
+      </c>
+      <c r="C140" s="95">
+        <v>21.4</v>
+      </c>
+      <c r="D140" s="96">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="E140" s="98">
+        <v>1830</v>
+      </c>
+      <c r="F140" s="98">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A141" s="97" t="s">
+        <v>248</v>
+      </c>
+      <c r="B141" s="95">
+        <v>73</v>
+      </c>
+      <c r="C141" s="95">
+        <v>21.2</v>
+      </c>
+      <c r="D141" s="96">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="E141" s="98">
+        <v>1600</v>
+      </c>
+      <c r="F141" s="98">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A142" s="97" t="s">
+        <v>247</v>
+      </c>
+      <c r="B142" s="95">
+        <v>68</v>
+      </c>
+      <c r="C142" s="95">
+        <v>21.1</v>
+      </c>
+      <c r="D142" s="96">
+        <v>0.43</v>
+      </c>
+      <c r="E142" s="98">
+        <v>1480</v>
+      </c>
+      <c r="F142" s="98">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A143" s="97" t="s">
+        <v>246</v>
+      </c>
+      <c r="B143" s="95">
+        <v>62</v>
+      </c>
+      <c r="C143" s="95">
+        <v>21</v>
+      </c>
+      <c r="D143" s="96">
+        <v>0.4</v>
+      </c>
+      <c r="E143" s="98">
+        <v>1330</v>
+      </c>
+      <c r="F143" s="98">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A144" s="97" t="s">
+        <v>245</v>
+      </c>
+      <c r="B144" s="95">
+        <v>55</v>
+      </c>
+      <c r="C144" s="95">
+        <v>20.8</v>
+      </c>
+      <c r="D144" s="96">
+        <v>0.375</v>
+      </c>
+      <c r="E144" s="98">
+        <v>1140</v>
+      </c>
+      <c r="F144" s="98">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A145" s="97" t="s">
+        <v>244</v>
+      </c>
+      <c r="B145" s="95">
+        <v>48</v>
+      </c>
+      <c r="C145" s="95">
+        <v>20.6</v>
+      </c>
+      <c r="D145" s="96">
+        <v>0.35</v>
+      </c>
+      <c r="E145" s="98">
+        <v>959</v>
+      </c>
+      <c r="F145" s="98">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A146" s="97" t="s">
+        <v>243</v>
+      </c>
+      <c r="B146" s="95">
+        <v>57</v>
+      </c>
+      <c r="C146" s="95">
+        <v>21.1</v>
+      </c>
+      <c r="D146" s="96">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="E146" s="98">
+        <v>1170</v>
+      </c>
+      <c r="F146" s="98">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A147" s="97" t="s">
+        <v>242</v>
+      </c>
+      <c r="B147" s="95">
+        <v>50</v>
+      </c>
+      <c r="C147" s="95">
+        <v>20.8</v>
+      </c>
+      <c r="D147" s="96">
+        <v>0.38</v>
+      </c>
+      <c r="E147" s="98">
+        <v>984</v>
+      </c>
+      <c r="F147" s="98">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A148" s="97" t="s">
+        <v>241</v>
+      </c>
+      <c r="B148" s="95">
+        <v>44</v>
+      </c>
+      <c r="C148" s="95">
+        <v>20.7</v>
+      </c>
+      <c r="D148" s="96">
+        <v>0.35</v>
+      </c>
+      <c r="E148" s="98">
+        <v>843</v>
+      </c>
+      <c r="F148" s="95">
+        <v>95.4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A149" s="97" t="s">
+        <v>240</v>
+      </c>
+      <c r="B149" s="98">
+        <v>311</v>
+      </c>
+      <c r="C149" s="95">
+        <v>22.3</v>
+      </c>
+      <c r="D149" s="94">
+        <v>1.52</v>
+      </c>
+      <c r="E149" s="98">
+        <v>6970</v>
+      </c>
+      <c r="F149" s="98">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A150" s="97" t="s">
+        <v>239</v>
+      </c>
+      <c r="B150" s="98">
+        <v>283</v>
+      </c>
+      <c r="C150" s="95">
+        <v>21.9</v>
+      </c>
+      <c r="D150" s="94">
+        <v>1.4</v>
+      </c>
+      <c r="E150" s="98">
+        <v>6170</v>
+      </c>
+      <c r="F150" s="98">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A151" s="97" t="s">
+        <v>238</v>
+      </c>
+      <c r="B151" s="98">
+        <v>258</v>
+      </c>
+      <c r="C151" s="95">
+        <v>21.5</v>
+      </c>
+      <c r="D151" s="94">
+        <v>1.28</v>
+      </c>
+      <c r="E151" s="98">
+        <v>5510</v>
+      </c>
+      <c r="F151" s="98">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A152" s="97" t="s">
+        <v>237</v>
+      </c>
+      <c r="B152" s="98">
+        <v>234</v>
+      </c>
+      <c r="C152" s="95">
+        <v>21.1</v>
+      </c>
+      <c r="D152" s="94">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="E152" s="98">
+        <v>4900</v>
+      </c>
+      <c r="F152" s="98">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A153" s="97" t="s">
+        <v>236</v>
+      </c>
+      <c r="B153" s="98">
+        <v>211</v>
+      </c>
+      <c r="C153" s="95">
+        <v>20.7</v>
+      </c>
+      <c r="D153" s="94">
+        <v>1.06</v>
+      </c>
+      <c r="E153" s="98">
+        <v>4330</v>
+      </c>
+      <c r="F153" s="98">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A154" s="97" t="s">
+        <v>235</v>
+      </c>
+      <c r="B154" s="98">
+        <v>192</v>
+      </c>
+      <c r="C154" s="95">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="D154" s="96">
+        <v>0.96</v>
+      </c>
+      <c r="E154" s="98">
+        <v>3870</v>
+      </c>
+      <c r="F154" s="98">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A155" s="97" t="s">
+        <v>234</v>
+      </c>
+      <c r="B155" s="98">
+        <v>175</v>
+      </c>
+      <c r="C155" s="95">
+        <v>20</v>
+      </c>
+      <c r="D155" s="96">
+        <v>0.89</v>
+      </c>
+      <c r="E155" s="98">
+        <v>3450</v>
+      </c>
+      <c r="F155" s="98">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A156" s="97" t="s">
+        <v>233</v>
+      </c>
+      <c r="B156" s="98">
+        <v>158</v>
+      </c>
+      <c r="C156" s="95">
+        <v>19.7</v>
+      </c>
+      <c r="D156" s="96">
+        <v>0.81</v>
+      </c>
+      <c r="E156" s="98">
+        <v>3060</v>
+      </c>
+      <c r="F156" s="98">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A157" s="97" t="s">
+        <v>232</v>
+      </c>
+      <c r="B157" s="98">
+        <v>143</v>
+      </c>
+      <c r="C157" s="95">
+        <v>19.5</v>
+      </c>
+      <c r="D157" s="96">
+        <v>0.73</v>
+      </c>
+      <c r="E157" s="98">
+        <v>2750</v>
+      </c>
+      <c r="F157" s="98">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A158" s="97" t="s">
+        <v>231</v>
+      </c>
+      <c r="B158" s="98">
+        <v>130</v>
+      </c>
+      <c r="C158" s="95">
+        <v>19.3</v>
+      </c>
+      <c r="D158" s="96">
+        <v>0.67</v>
+      </c>
+      <c r="E158" s="98">
+        <v>2460</v>
+      </c>
+      <c r="F158" s="98">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A159" s="97" t="s">
+        <v>230</v>
+      </c>
+      <c r="B159" s="98">
+        <v>119</v>
+      </c>
+      <c r="C159" s="95">
+        <v>19</v>
+      </c>
+      <c r="D159" s="96">
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="E159" s="98">
+        <v>2190</v>
+      </c>
+      <c r="F159" s="98">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A160" s="97" t="s">
+        <v>229</v>
+      </c>
+      <c r="B160" s="98">
+        <v>106</v>
+      </c>
+      <c r="C160" s="95">
+        <v>18.7</v>
+      </c>
+      <c r="D160" s="96">
+        <v>0.59</v>
+      </c>
+      <c r="E160" s="98">
+        <v>1910</v>
+      </c>
+      <c r="F160" s="98">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A161" s="97" t="s">
+        <v>228</v>
+      </c>
+      <c r="B161" s="95">
+        <v>97</v>
+      </c>
+      <c r="C161" s="95">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="D161" s="96">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="E161" s="98">
+        <v>1750</v>
+      </c>
+      <c r="F161" s="98">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A162" s="97" t="s">
+        <v>227</v>
+      </c>
+      <c r="B162" s="95">
+        <v>86</v>
+      </c>
+      <c r="C162" s="95">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="D162" s="96">
+        <v>0.48</v>
+      </c>
+      <c r="E162" s="98">
+        <v>1530</v>
+      </c>
+      <c r="F162" s="98">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A163" s="97" t="s">
+        <v>226</v>
+      </c>
+      <c r="B163" s="95">
+        <v>76</v>
+      </c>
+      <c r="C163" s="95">
+        <v>18.2</v>
+      </c>
+      <c r="D163" s="96">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="E163" s="98">
+        <v>1330</v>
+      </c>
+      <c r="F163" s="98">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A164" s="97" t="s">
+        <v>225</v>
+      </c>
+      <c r="B164" s="95">
+        <v>71</v>
+      </c>
+      <c r="C164" s="95">
+        <v>18.5</v>
+      </c>
+      <c r="D164" s="96">
+        <v>0.495</v>
+      </c>
+      <c r="E164" s="98">
+        <v>1170</v>
+      </c>
+      <c r="F164" s="98">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A165" s="97" t="s">
+        <v>224</v>
+      </c>
+      <c r="B165" s="95">
+        <v>65</v>
+      </c>
+      <c r="C165" s="95">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="D165" s="96">
+        <v>0.45</v>
+      </c>
+      <c r="E165" s="98">
+        <v>1070</v>
+      </c>
+      <c r="F165" s="98">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A166" s="97" t="s">
+        <v>223</v>
+      </c>
+      <c r="B166" s="95">
+        <v>60</v>
+      </c>
+      <c r="C166" s="95">
+        <v>18.2</v>
+      </c>
+      <c r="D166" s="96">
+        <v>0.41499999999999998</v>
+      </c>
+      <c r="E166" s="98">
+        <v>984</v>
+      </c>
+      <c r="F166" s="98">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A167" s="97" t="s">
+        <v>222</v>
+      </c>
+      <c r="B167" s="95">
+        <v>55</v>
+      </c>
+      <c r="C167" s="95">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="D167" s="96">
+        <v>0.39</v>
+      </c>
+      <c r="E167" s="98">
+        <v>890</v>
+      </c>
+      <c r="F167" s="98">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A168" s="97" t="s">
+        <v>221</v>
+      </c>
+      <c r="B168" s="95">
+        <v>50</v>
+      </c>
+      <c r="C168" s="95">
+        <v>18</v>
+      </c>
+      <c r="D168" s="96">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="E168" s="98">
+        <v>800</v>
+      </c>
+      <c r="F168" s="98">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A169" s="97" t="s">
+        <v>220</v>
+      </c>
+      <c r="B169" s="95">
+        <v>46</v>
+      </c>
+      <c r="C169" s="95">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="D169" s="96">
+        <v>0.36</v>
+      </c>
+      <c r="E169" s="98">
+        <v>712</v>
+      </c>
+      <c r="F169" s="95">
+        <v>90.7</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A170" s="97" t="s">
+        <v>219</v>
+      </c>
+      <c r="B170" s="95">
+        <v>40</v>
+      </c>
+      <c r="C170" s="95">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="D170" s="96">
+        <v>0.315</v>
+      </c>
+      <c r="E170" s="98">
+        <v>612</v>
+      </c>
+      <c r="F170" s="95">
+        <v>78.400000000000006</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A171" s="97" t="s">
+        <v>218</v>
+      </c>
+      <c r="B171" s="95">
+        <v>35</v>
+      </c>
+      <c r="C171" s="95">
+        <v>17.7</v>
+      </c>
+      <c r="D171" s="96">
+        <v>0.3</v>
+      </c>
+      <c r="E171" s="98">
+        <v>510</v>
+      </c>
+      <c r="F171" s="95">
+        <v>66.5</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A172" s="97" t="s">
+        <v>217</v>
+      </c>
+      <c r="B172" s="98">
+        <v>100</v>
+      </c>
+      <c r="C172" s="95">
+        <v>17</v>
+      </c>
+      <c r="D172" s="96">
+        <v>0.58499999999999996</v>
+      </c>
+      <c r="E172" s="98">
+        <v>1490</v>
+      </c>
+      <c r="F172" s="98">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A173" s="97" t="s">
+        <v>216</v>
+      </c>
+      <c r="B173" s="95">
+        <v>89</v>
+      </c>
+      <c r="C173" s="95">
+        <v>16.8</v>
+      </c>
+      <c r="D173" s="96">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E173" s="98">
+        <v>1300</v>
+      </c>
+      <c r="F173" s="98">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A174" s="97" t="s">
+        <v>215</v>
+      </c>
+      <c r="B174" s="95">
+        <v>77</v>
+      </c>
+      <c r="C174" s="95">
+        <v>16.5</v>
+      </c>
+      <c r="D174" s="96">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="E174" s="98">
+        <v>1110</v>
+      </c>
+      <c r="F174" s="98">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A175" s="97" t="s">
+        <v>214</v>
+      </c>
+      <c r="B175" s="95">
+        <v>67</v>
+      </c>
+      <c r="C175" s="95">
+        <v>16.3</v>
+      </c>
+      <c r="D175" s="96">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="E175" s="98">
+        <v>954</v>
+      </c>
+      <c r="F175" s="98">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A176" s="97" t="s">
+        <v>213</v>
+      </c>
+      <c r="B176" s="95">
+        <v>57</v>
+      </c>
+      <c r="C176" s="95">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="D176" s="96">
+        <v>0.43</v>
+      </c>
+      <c r="E176" s="98">
+        <v>758</v>
+      </c>
+      <c r="F176" s="98">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A177" s="97" t="s">
+        <v>212</v>
+      </c>
+      <c r="B177" s="95">
+        <v>50</v>
+      </c>
+      <c r="C177" s="95">
+        <v>16.3</v>
+      </c>
+      <c r="D177" s="96">
+        <v>0.38</v>
+      </c>
+      <c r="E177" s="98">
+        <v>659</v>
+      </c>
+      <c r="F177" s="95">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A178" s="97" t="s">
+        <v>211</v>
+      </c>
+      <c r="B178" s="95">
+        <v>45</v>
+      </c>
+      <c r="C178" s="95">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="D178" s="96">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="E178" s="98">
+        <v>586</v>
+      </c>
+      <c r="F178" s="95">
+        <v>82.3</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A179" s="97" t="s">
+        <v>210</v>
+      </c>
+      <c r="B179" s="95">
+        <v>40</v>
+      </c>
+      <c r="C179" s="95">
+        <v>16</v>
+      </c>
+      <c r="D179" s="96">
+        <v>0.30499999999999999</v>
+      </c>
+      <c r="E179" s="98">
+        <v>518</v>
+      </c>
+      <c r="F179" s="95">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A180" s="97" t="s">
+        <v>209</v>
+      </c>
+      <c r="B180" s="95">
+        <v>36</v>
+      </c>
+      <c r="C180" s="95">
+        <v>15.9</v>
+      </c>
+      <c r="D180" s="96">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="E180" s="98">
+        <v>448</v>
+      </c>
+      <c r="F180" s="95">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A181" s="97" t="s">
+        <v>208</v>
+      </c>
+      <c r="B181" s="95">
+        <v>31</v>
+      </c>
+      <c r="C181" s="95">
+        <v>15.9</v>
+      </c>
+      <c r="D181" s="96">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="E181" s="98">
+        <v>375</v>
+      </c>
+      <c r="F181" s="95">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A182" s="97" t="s">
+        <v>207</v>
+      </c>
+      <c r="B182" s="95">
+        <v>26</v>
+      </c>
+      <c r="C182" s="95">
+        <v>15.7</v>
+      </c>
+      <c r="D182" s="96">
+        <v>0.25</v>
+      </c>
+      <c r="E182" s="98">
+        <v>301</v>
+      </c>
+      <c r="F182" s="95">
+        <v>44.2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A183" s="97" t="s">
+        <v>206</v>
+      </c>
+      <c r="B183" s="98">
+        <v>873</v>
+      </c>
+      <c r="C183" s="95">
+        <v>23.6</v>
+      </c>
+      <c r="D183" s="94">
+        <v>3.94</v>
+      </c>
+      <c r="E183" s="98">
+        <v>18100</v>
+      </c>
+      <c r="F183" s="98">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A184" s="97" t="s">
+        <v>205</v>
+      </c>
+      <c r="B184" s="98">
+        <v>808</v>
+      </c>
+      <c r="C184" s="95">
+        <v>22.8</v>
+      </c>
+      <c r="D184" s="94">
+        <v>3.74</v>
+      </c>
+      <c r="E184" s="98">
+        <v>15900</v>
+      </c>
+      <c r="F184" s="98">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A185" s="97" t="s">
+        <v>204</v>
+      </c>
+      <c r="B185" s="98">
+        <v>730</v>
+      </c>
+      <c r="C185" s="95">
+        <v>22.4</v>
+      </c>
+      <c r="D185" s="94">
+        <v>3.07</v>
+      </c>
+      <c r="E185" s="98">
+        <v>14300</v>
+      </c>
+      <c r="F185" s="98">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A186" s="97" t="s">
+        <v>203</v>
+      </c>
+      <c r="B186" s="98">
+        <v>665</v>
+      </c>
+      <c r="C186" s="95">
+        <v>21.6</v>
+      </c>
+      <c r="D186" s="94">
+        <v>2.83</v>
+      </c>
+      <c r="E186" s="98">
+        <v>12400</v>
+      </c>
+      <c r="F186" s="98">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A187" s="97" t="s">
+        <v>202</v>
+      </c>
+      <c r="B187" s="98">
+        <v>605</v>
+      </c>
+      <c r="C187" s="95">
+        <v>20.9</v>
+      </c>
+      <c r="D187" s="94">
+        <v>2.6</v>
+      </c>
+      <c r="E187" s="98">
+        <v>10800</v>
+      </c>
+      <c r="F187" s="98">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A188" s="97" t="s">
+        <v>201</v>
+      </c>
+      <c r="B188" s="98">
+        <v>550</v>
+      </c>
+      <c r="C188" s="95">
+        <v>20.2</v>
+      </c>
+      <c r="D188" s="94">
+        <v>2.38</v>
+      </c>
+      <c r="E188" s="98">
+        <v>9430</v>
+      </c>
+      <c r="F188" s="98">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A189" s="97" t="s">
+        <v>200</v>
+      </c>
+      <c r="B189" s="98">
+        <v>500</v>
+      </c>
+      <c r="C189" s="95">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="D189" s="94">
+        <v>2.19</v>
+      </c>
+      <c r="E189" s="98">
+        <v>8210</v>
+      </c>
+      <c r="F189" s="98">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A190" s="97" t="s">
+        <v>199</v>
+      </c>
+      <c r="B190" s="98">
+        <v>455</v>
+      </c>
+      <c r="C190" s="95">
+        <v>19</v>
+      </c>
+      <c r="D190" s="94">
+        <v>2.02</v>
+      </c>
+      <c r="E190" s="98">
+        <v>7190</v>
+      </c>
+      <c r="F190" s="98">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A191" s="97" t="s">
+        <v>198</v>
+      </c>
+      <c r="B191" s="98">
+        <v>426</v>
+      </c>
+      <c r="C191" s="95">
+        <v>18.7</v>
+      </c>
+      <c r="D191" s="94">
+        <v>1.88</v>
+      </c>
+      <c r="E191" s="98">
+        <v>6600</v>
+      </c>
+      <c r="F191" s="98">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A192" s="97" t="s">
+        <v>197</v>
+      </c>
+      <c r="B192" s="98">
+        <v>398</v>
+      </c>
+      <c r="C192" s="95">
+        <v>18.3</v>
+      </c>
+      <c r="D192" s="94">
+        <v>1.77</v>
+      </c>
+      <c r="E192" s="98">
+        <v>6000</v>
+      </c>
+      <c r="F192" s="98">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A193" s="97" t="s">
+        <v>196</v>
+      </c>
+      <c r="B193" s="98">
+        <v>370</v>
+      </c>
+      <c r="C193" s="95">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="D193" s="94">
+        <v>1.66</v>
+      </c>
+      <c r="E193" s="98">
+        <v>5440</v>
+      </c>
+      <c r="F193" s="98">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A194" s="97" t="s">
+        <v>195</v>
+      </c>
+      <c r="B194" s="98">
+        <v>342</v>
+      </c>
+      <c r="C194" s="95">
+        <v>17.5</v>
+      </c>
+      <c r="D194" s="94">
+        <v>1.54</v>
+      </c>
+      <c r="E194" s="98">
+        <v>4900</v>
+      </c>
+      <c r="F194" s="98">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A195" s="97" t="s">
+        <v>194</v>
+      </c>
+      <c r="B195" s="98">
+        <v>311</v>
+      </c>
+      <c r="C195" s="95">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="D195" s="94">
+        <v>1.41</v>
+      </c>
+      <c r="E195" s="98">
+        <v>4330</v>
+      </c>
+      <c r="F195" s="98">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A196" s="97" t="s">
+        <v>193</v>
+      </c>
+      <c r="B196" s="98">
+        <v>283</v>
+      </c>
+      <c r="C196" s="95">
+        <v>16.7</v>
+      </c>
+      <c r="D196" s="94">
+        <v>1.29</v>
+      </c>
+      <c r="E196" s="98">
+        <v>3840</v>
+      </c>
+      <c r="F196" s="98">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A197" s="97" t="s">
+        <v>192</v>
+      </c>
+      <c r="B197" s="98">
+        <v>257</v>
+      </c>
+      <c r="C197" s="95">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="D197" s="94">
+        <v>1.18</v>
+      </c>
+      <c r="E197" s="98">
+        <v>3400</v>
+      </c>
+      <c r="F197" s="98">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A198" s="97" t="s">
+        <v>191</v>
+      </c>
+      <c r="B198" s="98">
+        <v>233</v>
+      </c>
+      <c r="C198" s="95">
+        <v>16</v>
+      </c>
+      <c r="D198" s="94">
+        <v>1.07</v>
+      </c>
+      <c r="E198" s="98">
+        <v>3010</v>
+      </c>
+      <c r="F198" s="98">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A199" s="97" t="s">
+        <v>190</v>
+      </c>
+      <c r="B199" s="98">
+        <v>211</v>
+      </c>
+      <c r="C199" s="95">
+        <v>15.7</v>
+      </c>
+      <c r="D199" s="96">
+        <v>0.98</v>
+      </c>
+      <c r="E199" s="98">
+        <v>2660</v>
+      </c>
+      <c r="F199" s="98">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A200" s="97" t="s">
+        <v>189</v>
+      </c>
+      <c r="B200" s="98">
+        <v>193</v>
+      </c>
+      <c r="C200" s="95">
+        <v>15.5</v>
+      </c>
+      <c r="D200" s="96">
+        <v>0.89</v>
+      </c>
+      <c r="E200" s="98">
+        <v>2400</v>
+      </c>
+      <c r="F200" s="98">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A201" s="97" t="s">
+        <v>188</v>
+      </c>
+      <c r="B201" s="98">
+        <v>176</v>
+      </c>
+      <c r="C201" s="95">
+        <v>15.2</v>
+      </c>
+      <c r="D201" s="96">
+        <v>0.83</v>
+      </c>
+      <c r="E201" s="98">
+        <v>2140</v>
+      </c>
+      <c r="F201" s="98">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A202" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="B202" s="98">
+        <v>159</v>
+      </c>
+      <c r="C202" s="95">
+        <v>15</v>
+      </c>
+      <c r="D202" s="96">
+        <v>0.745</v>
+      </c>
+      <c r="E202" s="98">
+        <v>1900</v>
+      </c>
+      <c r="F202" s="98">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A203" s="97" t="s">
+        <v>186</v>
+      </c>
+      <c r="B203" s="98">
+        <v>145</v>
+      </c>
+      <c r="C203" s="95">
+        <v>14.8</v>
+      </c>
+      <c r="D203" s="96">
+        <v>0.68</v>
+      </c>
+      <c r="E203" s="98">
+        <v>1710</v>
+      </c>
+      <c r="F203" s="98">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A204" s="97" t="s">
+        <v>185</v>
+      </c>
+      <c r="B204" s="98">
+        <v>132</v>
+      </c>
+      <c r="C204" s="95">
+        <v>14.7</v>
+      </c>
+      <c r="D204" s="96">
+        <v>0.64500000000000002</v>
+      </c>
+      <c r="E204" s="98">
+        <v>1530</v>
+      </c>
+      <c r="F204" s="98">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A205" s="97" t="s">
+        <v>184</v>
+      </c>
+      <c r="B205" s="98">
+        <v>120</v>
+      </c>
+      <c r="C205" s="95">
+        <v>14.5</v>
+      </c>
+      <c r="D205" s="96">
+        <v>0.59</v>
+      </c>
+      <c r="E205" s="98">
+        <v>1380</v>
+      </c>
+      <c r="F205" s="98">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A206" s="97" t="s">
+        <v>183</v>
+      </c>
+      <c r="B206" s="98">
+        <v>109</v>
+      </c>
+      <c r="C206" s="95">
+        <v>14.3</v>
+      </c>
+      <c r="D206" s="96">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E206" s="98">
+        <v>1240</v>
+      </c>
+      <c r="F206" s="98">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A207" s="97" t="s">
+        <v>182</v>
+      </c>
+      <c r="B207" s="95">
+        <v>99</v>
+      </c>
+      <c r="C207" s="95">
+        <v>14.2</v>
+      </c>
+      <c r="D207" s="96">
+        <v>0.48499999999999999</v>
+      </c>
+      <c r="E207" s="98">
+        <v>1110</v>
+      </c>
+      <c r="F207" s="98">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A208" s="97" t="s">
+        <v>181</v>
+      </c>
+      <c r="B208" s="95">
+        <v>90</v>
+      </c>
+      <c r="C208" s="95">
+        <v>14</v>
+      </c>
+      <c r="D208" s="96">
+        <v>0.44</v>
+      </c>
+      <c r="E208" s="98">
+        <v>999</v>
+      </c>
+      <c r="F208" s="98">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A209" s="97" t="s">
+        <v>180</v>
+      </c>
+      <c r="B209" s="95">
+        <v>82</v>
+      </c>
+      <c r="C209" s="95">
+        <v>14.3</v>
+      </c>
+      <c r="D209" s="96">
+        <v>0.51</v>
+      </c>
+      <c r="E209" s="98">
+        <v>881</v>
+      </c>
+      <c r="F209" s="98">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A210" s="97" t="s">
+        <v>179</v>
+      </c>
+      <c r="B210" s="95">
+        <v>74</v>
+      </c>
+      <c r="C210" s="95">
+        <v>14.2</v>
+      </c>
+      <c r="D210" s="96">
+        <v>0.45</v>
+      </c>
+      <c r="E210" s="98">
+        <v>795</v>
+      </c>
+      <c r="F210" s="98">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A211" s="97" t="s">
+        <v>178</v>
+      </c>
+      <c r="B211" s="95">
+        <v>68</v>
+      </c>
+      <c r="C211" s="95">
+        <v>14</v>
+      </c>
+      <c r="D211" s="96">
+        <v>0.41499999999999998</v>
+      </c>
+      <c r="E211" s="98">
+        <v>722</v>
+      </c>
+      <c r="F211" s="98">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A212" s="97" t="s">
+        <v>177</v>
+      </c>
+      <c r="B212" s="95">
+        <v>61</v>
+      </c>
+      <c r="C212" s="95">
+        <v>13.9</v>
+      </c>
+      <c r="D212" s="96">
+        <v>0.375</v>
+      </c>
+      <c r="E212" s="98">
+        <v>640</v>
+      </c>
+      <c r="F212" s="98">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A213" s="97" t="s">
+        <v>176</v>
+      </c>
+      <c r="B213" s="95">
+        <v>53</v>
+      </c>
+      <c r="C213" s="95">
+        <v>13.9</v>
+      </c>
+      <c r="D213" s="96">
+        <v>0.37</v>
+      </c>
+      <c r="E213" s="98">
+        <v>541</v>
+      </c>
+      <c r="F213" s="95">
+        <v>87.1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A214" s="97" t="s">
+        <v>175</v>
+      </c>
+      <c r="B214" s="95">
+        <v>48</v>
+      </c>
+      <c r="C214" s="95">
+        <v>13.8</v>
+      </c>
+      <c r="D214" s="96">
+        <v>0.34</v>
+      </c>
+      <c r="E214" s="98">
+        <v>484</v>
+      </c>
+      <c r="F214" s="95">
+        <v>78.400000000000006</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A215" s="97" t="s">
+        <v>174</v>
+      </c>
+      <c r="B215" s="95">
+        <v>43</v>
+      </c>
+      <c r="C215" s="95">
+        <v>13.7</v>
+      </c>
+      <c r="D215" s="96">
+        <v>0.30499999999999999</v>
+      </c>
+      <c r="E215" s="98">
+        <v>428</v>
+      </c>
+      <c r="F215" s="95">
+        <v>69.599999999999994</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A216" s="97" t="s">
+        <v>173</v>
+      </c>
+      <c r="B216" s="95">
+        <v>38</v>
+      </c>
+      <c r="C216" s="95">
+        <v>14.1</v>
+      </c>
+      <c r="D216" s="96">
+        <v>0.31</v>
+      </c>
+      <c r="E216" s="98">
+        <v>385</v>
+      </c>
+      <c r="F216" s="95">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A217" s="97" t="s">
+        <v>172</v>
+      </c>
+      <c r="B217" s="95">
+        <v>34</v>
+      </c>
+      <c r="C217" s="95">
+        <v>14</v>
+      </c>
+      <c r="D217" s="96">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="E217" s="98">
+        <v>340</v>
+      </c>
+      <c r="F217" s="95">
+        <v>54.6</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A218" s="97" t="s">
+        <v>171</v>
+      </c>
+      <c r="B218" s="95">
+        <v>30</v>
+      </c>
+      <c r="C218" s="95">
+        <v>13.8</v>
+      </c>
+      <c r="D218" s="96">
+        <v>0.27</v>
+      </c>
+      <c r="E218" s="98">
+        <v>291</v>
+      </c>
+      <c r="F218" s="95">
+        <v>47.3</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A219" s="97" t="s">
+        <v>170</v>
+      </c>
+      <c r="B219" s="95">
+        <v>26</v>
+      </c>
+      <c r="C219" s="95">
+        <v>13.9</v>
+      </c>
+      <c r="D219" s="96">
+        <v>0.255</v>
+      </c>
+      <c r="E219" s="98">
+        <v>245</v>
+      </c>
+      <c r="F219" s="95">
+        <v>40.200000000000003</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A220" s="97" t="s">
+        <v>169</v>
+      </c>
+      <c r="B220" s="95">
+        <v>22</v>
+      </c>
+      <c r="C220" s="95">
+        <v>13.7</v>
+      </c>
+      <c r="D220" s="96">
+        <v>0.23</v>
+      </c>
+      <c r="E220" s="98">
+        <v>199</v>
+      </c>
+      <c r="F220" s="95">
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A221" s="97" t="s">
+        <v>168</v>
+      </c>
+      <c r="B221" s="98">
+        <v>336</v>
+      </c>
+      <c r="C221" s="95">
+        <v>16.8</v>
+      </c>
+      <c r="D221" s="94">
+        <v>1.78</v>
+      </c>
+      <c r="E221" s="98">
+        <v>4060</v>
+      </c>
+      <c r="F221" s="98">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A222" s="97" t="s">
+        <v>167</v>
+      </c>
+      <c r="B222" s="98">
+        <v>305</v>
+      </c>
+      <c r="C222" s="95">
+        <v>16.3</v>
+      </c>
+      <c r="D222" s="94">
+        <v>1.63</v>
+      </c>
+      <c r="E222" s="98">
+        <v>3550</v>
+      </c>
+      <c r="F222" s="98">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A223" s="97" t="s">
+        <v>166</v>
+      </c>
+      <c r="B223" s="98">
+        <v>279</v>
+      </c>
+      <c r="C223" s="95">
+        <v>15.9</v>
+      </c>
+      <c r="D223" s="94">
+        <v>1.53</v>
+      </c>
+      <c r="E223" s="98">
+        <v>3110</v>
+      </c>
+      <c r="F223" s="98">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A224" s="97" t="s">
+        <v>165</v>
+      </c>
+      <c r="B224" s="98">
+        <v>252</v>
+      </c>
+      <c r="C224" s="95">
+        <v>15.4</v>
+      </c>
+      <c r="D224" s="94">
+        <v>1.4</v>
+      </c>
+      <c r="E224" s="98">
+        <v>2720</v>
+      </c>
+      <c r="F224" s="98">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A225" s="97" t="s">
+        <v>164</v>
+      </c>
+      <c r="B225" s="98">
+        <v>230</v>
+      </c>
+      <c r="C225" s="95">
+        <v>15.1</v>
+      </c>
+      <c r="D225" s="94">
+        <v>1.29</v>
+      </c>
+      <c r="E225" s="98">
+        <v>2420</v>
+      </c>
+      <c r="F225" s="98">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A226" s="97" t="s">
+        <v>163</v>
+      </c>
+      <c r="B226" s="98">
+        <v>210</v>
+      </c>
+      <c r="C226" s="95">
+        <v>14.7</v>
+      </c>
+      <c r="D226" s="94">
+        <v>1.18</v>
+      </c>
+      <c r="E226" s="98">
+        <v>2140</v>
+      </c>
+      <c r="F226" s="98">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A227" s="97" t="s">
+        <v>162</v>
+      </c>
+      <c r="B227" s="98">
+        <v>190</v>
+      </c>
+      <c r="C227" s="95">
+        <v>14.4</v>
+      </c>
+      <c r="D227" s="94">
+        <v>1.06</v>
+      </c>
+      <c r="E227" s="98">
+        <v>1890</v>
+      </c>
+      <c r="F227" s="98">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A228" s="97" t="s">
+        <v>161</v>
+      </c>
+      <c r="B228" s="98">
+        <v>170</v>
+      </c>
+      <c r="C228" s="95">
+        <v>14</v>
+      </c>
+      <c r="D228" s="96">
+        <v>0.96</v>
+      </c>
+      <c r="E228" s="98">
+        <v>1650</v>
+      </c>
+      <c r="F228" s="98">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A229" s="97" t="s">
+        <v>160</v>
+      </c>
+      <c r="B229" s="98">
+        <v>152</v>
+      </c>
+      <c r="C229" s="95">
+        <v>13.7</v>
+      </c>
+      <c r="D229" s="96">
+        <v>0.87</v>
+      </c>
+      <c r="E229" s="98">
+        <v>1430</v>
+      </c>
+      <c r="F229" s="98">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A230" s="97" t="s">
+        <v>159</v>
+      </c>
+      <c r="B230" s="98">
+        <v>136</v>
+      </c>
+      <c r="C230" s="95">
+        <v>13.4</v>
+      </c>
+      <c r="D230" s="96">
+        <v>0.79</v>
+      </c>
+      <c r="E230" s="98">
+        <v>1240</v>
+      </c>
+      <c r="F230" s="98">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A231" s="97" t="s">
+        <v>158</v>
+      </c>
+      <c r="B231" s="98">
+        <v>120</v>
+      </c>
+      <c r="C231" s="95">
+        <v>13.1</v>
+      </c>
+      <c r="D231" s="96">
+        <v>0.71</v>
+      </c>
+      <c r="E231" s="98">
+        <v>1070</v>
+      </c>
+      <c r="F231" s="98">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A232" s="97" t="s">
+        <v>157</v>
+      </c>
+      <c r="B232" s="98">
+        <v>106</v>
+      </c>
+      <c r="C232" s="95">
+        <v>12.9</v>
+      </c>
+      <c r="D232" s="96">
+        <v>0.61</v>
+      </c>
+      <c r="E232" s="98">
+        <v>933</v>
+      </c>
+      <c r="F232" s="98">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A233" s="97" t="s">
+        <v>156</v>
+      </c>
+      <c r="B233" s="95">
+        <v>96</v>
+      </c>
+      <c r="C233" s="95">
+        <v>12.7</v>
+      </c>
+      <c r="D233" s="96">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E233" s="98">
+        <v>833</v>
+      </c>
+      <c r="F233" s="98">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A234" s="97" t="s">
+        <v>155</v>
+      </c>
+      <c r="B234" s="95">
+        <v>87</v>
+      </c>
+      <c r="C234" s="95">
+        <v>12.5</v>
+      </c>
+      <c r="D234" s="96">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="E234" s="98">
+        <v>740</v>
+      </c>
+      <c r="F234" s="98">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A235" s="97" t="s">
+        <v>154</v>
+      </c>
+      <c r="B235" s="95">
+        <v>79</v>
+      </c>
+      <c r="C235" s="95">
+        <v>12.4</v>
+      </c>
+      <c r="D235" s="96">
+        <v>0.47</v>
+      </c>
+      <c r="E235" s="98">
+        <v>662</v>
+      </c>
+      <c r="F235" s="98">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A236" s="97" t="s">
+        <v>153</v>
+      </c>
+      <c r="B236" s="95">
+        <v>72</v>
+      </c>
+      <c r="C236" s="95">
+        <v>12.3</v>
+      </c>
+      <c r="D236" s="96">
+        <v>0.43</v>
+      </c>
+      <c r="E236" s="98">
+        <v>597</v>
+      </c>
+      <c r="F236" s="98">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A237" s="97" t="s">
+        <v>152</v>
+      </c>
+      <c r="B237" s="95">
+        <v>65</v>
+      </c>
+      <c r="C237" s="95">
+        <v>12.1</v>
+      </c>
+      <c r="D237" s="96">
+        <v>0.39</v>
+      </c>
+      <c r="E237" s="98">
+        <v>533</v>
+      </c>
+      <c r="F237" s="95">
+        <v>96.8</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A238" s="97" t="s">
+        <v>151</v>
+      </c>
+      <c r="B238" s="95">
+        <v>58</v>
+      </c>
+      <c r="C238" s="95">
+        <v>12.2</v>
+      </c>
+      <c r="D238" s="96">
+        <v>0.36</v>
+      </c>
+      <c r="E238" s="98">
+        <v>475</v>
+      </c>
+      <c r="F238" s="95">
+        <v>86.4</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A239" s="97" t="s">
+        <v>150</v>
+      </c>
+      <c r="B239" s="95">
+        <v>53</v>
+      </c>
+      <c r="C239" s="95">
+        <v>12.1</v>
+      </c>
+      <c r="D239" s="96">
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="E239" s="98">
+        <v>425</v>
+      </c>
+      <c r="F239" s="95">
+        <v>77.900000000000006</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A240" s="97" t="s">
+        <v>149</v>
+      </c>
+      <c r="B240" s="95">
+        <v>50</v>
+      </c>
+      <c r="C240" s="95">
+        <v>12.2</v>
+      </c>
+      <c r="D240" s="96">
+        <v>0.37</v>
+      </c>
+      <c r="E240" s="98">
+        <v>391</v>
+      </c>
+      <c r="F240" s="95">
+        <v>71.900000000000006</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A241" s="97" t="s">
+        <v>148</v>
+      </c>
+      <c r="B241" s="95">
+        <v>45</v>
+      </c>
+      <c r="C241" s="95">
+        <v>12.1</v>
+      </c>
+      <c r="D241" s="96">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="E241" s="98">
+        <v>348</v>
+      </c>
+      <c r="F241" s="95">
+        <v>64.2</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A242" s="97" t="s">
+        <v>147</v>
+      </c>
+      <c r="B242" s="95">
+        <v>40</v>
+      </c>
+      <c r="C242" s="95">
+        <v>11.9</v>
+      </c>
+      <c r="D242" s="96">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="E242" s="98">
+        <v>307</v>
+      </c>
+      <c r="F242" s="95">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A243" s="97" t="s">
+        <v>146</v>
+      </c>
+      <c r="B243" s="95">
+        <v>35</v>
+      </c>
+      <c r="C243" s="95">
+        <v>12.5</v>
+      </c>
+      <c r="D243" s="96">
+        <v>0.3</v>
+      </c>
+      <c r="E243" s="98">
+        <v>285</v>
+      </c>
+      <c r="F243" s="95">
+        <v>51.2</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A244" s="97" t="s">
+        <v>145</v>
+      </c>
+      <c r="B244" s="95">
+        <v>30</v>
+      </c>
+      <c r="C244" s="95">
+        <v>12.3</v>
+      </c>
+      <c r="D244" s="96">
+        <v>0.26</v>
+      </c>
+      <c r="E244" s="98">
+        <v>238</v>
+      </c>
+      <c r="F244" s="95">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A245" s="97" t="s">
+        <v>144</v>
+      </c>
+      <c r="B245" s="95">
+        <v>26</v>
+      </c>
+      <c r="C245" s="95">
+        <v>12.2</v>
+      </c>
+      <c r="D245" s="96">
+        <v>0.23</v>
+      </c>
+      <c r="E245" s="98">
+        <v>204</v>
+      </c>
+      <c r="F245" s="95">
+        <v>37.200000000000003</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A246" s="97" t="s">
+        <v>143</v>
+      </c>
+      <c r="B246" s="95">
+        <v>22</v>
+      </c>
+      <c r="C246" s="95">
+        <v>12.3</v>
+      </c>
+      <c r="D246" s="96">
+        <v>0.26</v>
+      </c>
+      <c r="E246" s="98">
+        <v>156</v>
+      </c>
+      <c r="F246" s="95">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A247" s="97" t="s">
+        <v>142</v>
+      </c>
+      <c r="B247" s="95">
+        <v>19</v>
+      </c>
+      <c r="C247" s="95">
+        <v>12.2</v>
+      </c>
+      <c r="D247" s="96">
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="E247" s="98">
+        <v>130</v>
+      </c>
+      <c r="F247" s="95">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A248" s="97" t="s">
+        <v>141</v>
+      </c>
+      <c r="B248" s="95">
+        <v>16</v>
+      </c>
+      <c r="C248" s="95">
+        <v>12</v>
+      </c>
+      <c r="D248" s="96">
+        <v>0.22</v>
+      </c>
+      <c r="E248" s="98">
+        <v>103</v>
+      </c>
+      <c r="F248" s="95">
+        <v>20.100000000000001</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A249" s="97" t="s">
+        <v>140</v>
+      </c>
+      <c r="B249" s="95">
+        <v>14</v>
+      </c>
+      <c r="C249" s="95">
+        <v>11.9</v>
+      </c>
+      <c r="D249" s="96">
+        <v>0.2</v>
+      </c>
+      <c r="E249" s="95">
+        <v>88.6</v>
+      </c>
+      <c r="F249" s="95">
+        <v>17.399999999999999</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A250" s="97" t="s">
+        <v>139</v>
+      </c>
+      <c r="B250" s="98">
+        <v>112</v>
+      </c>
+      <c r="C250" s="95">
+        <v>11.4</v>
+      </c>
+      <c r="D250" s="96">
+        <v>0.755</v>
+      </c>
+      <c r="E250" s="98">
+        <v>716</v>
+      </c>
+      <c r="F250" s="98">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A251" s="97" t="s">
+        <v>138</v>
+      </c>
+      <c r="B251" s="98">
+        <v>100</v>
+      </c>
+      <c r="C251" s="95">
+        <v>11.1</v>
+      </c>
+      <c r="D251" s="96">
+        <v>0.68</v>
+      </c>
+      <c r="E251" s="98">
+        <v>623</v>
+      </c>
+      <c r="F251" s="98">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A252" s="97" t="s">
+        <v>137</v>
+      </c>
+      <c r="B252" s="95">
+        <v>88</v>
+      </c>
+      <c r="C252" s="95">
+        <v>10.8</v>
+      </c>
+      <c r="D252" s="96">
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="E252" s="98">
+        <v>534</v>
+      </c>
+      <c r="F252" s="98">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A253" s="97" t="s">
+        <v>136</v>
+      </c>
+      <c r="B253" s="95">
+        <v>77</v>
+      </c>
+      <c r="C253" s="95">
+        <v>10.6</v>
+      </c>
+      <c r="D253" s="96">
+        <v>0.53</v>
+      </c>
+      <c r="E253" s="98">
+        <v>455</v>
+      </c>
+      <c r="F253" s="95">
+        <v>97.6</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A254" s="97" t="s">
+        <v>135</v>
+      </c>
+      <c r="B254" s="95">
+        <v>68</v>
+      </c>
+      <c r="C254" s="95">
+        <v>10.4</v>
+      </c>
+      <c r="D254" s="96">
+        <v>0.47</v>
+      </c>
+      <c r="E254" s="98">
+        <v>394</v>
+      </c>
+      <c r="F254" s="95">
+        <v>85.3</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A255" s="97" t="s">
+        <v>134</v>
+      </c>
+      <c r="B255" s="95">
+        <v>60</v>
+      </c>
+      <c r="C255" s="95">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="D255" s="96">
+        <v>0.42</v>
+      </c>
+      <c r="E255" s="98">
+        <v>341</v>
+      </c>
+      <c r="F255" s="95">
+        <v>74.599999999999994</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A256" s="97" t="s">
+        <v>133</v>
+      </c>
+      <c r="B256" s="95">
+        <v>54</v>
+      </c>
+      <c r="C256" s="95">
+        <v>10.1</v>
+      </c>
+      <c r="D256" s="96">
+        <v>0.37</v>
+      </c>
+      <c r="E256" s="98">
+        <v>303</v>
+      </c>
+      <c r="F256" s="95">
+        <v>66.599999999999994</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A257" s="97" t="s">
+        <v>132</v>
+      </c>
+      <c r="B257" s="95">
+        <v>49</v>
+      </c>
+      <c r="C257" s="95">
+        <v>10</v>
+      </c>
+      <c r="D257" s="96">
+        <v>0.34</v>
+      </c>
+      <c r="E257" s="98">
+        <v>272</v>
+      </c>
+      <c r="F257" s="95">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A258" s="97" t="s">
+        <v>131</v>
+      </c>
+      <c r="B258" s="95">
+        <v>45</v>
+      </c>
+      <c r="C258" s="95">
+        <v>10.1</v>
+      </c>
+      <c r="D258" s="96">
+        <v>0.35</v>
+      </c>
+      <c r="E258" s="98">
+        <v>248</v>
+      </c>
+      <c r="F258" s="95">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A259" s="97" t="s">
+        <v>130</v>
+      </c>
+      <c r="B259" s="95">
+        <v>39</v>
+      </c>
+      <c r="C259" s="94">
+        <v>9.92</v>
+      </c>
+      <c r="D259" s="96">
+        <v>0.315</v>
+      </c>
+      <c r="E259" s="98">
+        <v>209</v>
+      </c>
+      <c r="F259" s="95">
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A260" s="97" t="s">
+        <v>129</v>
+      </c>
+      <c r="B260" s="95">
+        <v>33</v>
+      </c>
+      <c r="C260" s="94">
+        <v>9.73</v>
+      </c>
+      <c r="D260" s="96">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="E260" s="98">
+        <v>171</v>
+      </c>
+      <c r="F260" s="95">
+        <v>38.799999999999997</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A261" s="97" t="s">
+        <v>128</v>
+      </c>
+      <c r="B261" s="95">
+        <v>30</v>
+      </c>
+      <c r="C261" s="95">
+        <v>10.5</v>
+      </c>
+      <c r="D261" s="96">
+        <v>0.3</v>
+      </c>
+      <c r="E261" s="98">
+        <v>170</v>
+      </c>
+      <c r="F261" s="95">
+        <v>36.6</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A262" s="97" t="s">
+        <v>127</v>
+      </c>
+      <c r="B262" s="95">
+        <v>26</v>
+      </c>
+      <c r="C262" s="95">
+        <v>10.3</v>
+      </c>
+      <c r="D262" s="96">
+        <v>0.26</v>
+      </c>
+      <c r="E262" s="98">
+        <v>144</v>
+      </c>
+      <c r="F262" s="95">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A263" s="97" t="s">
+        <v>126</v>
+      </c>
+      <c r="B263" s="95">
+        <v>22</v>
+      </c>
+      <c r="C263" s="95">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="D263" s="96">
+        <v>0.24</v>
+      </c>
+      <c r="E263" s="98">
+        <v>118</v>
+      </c>
+      <c r="F263" s="95">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A264" s="97" t="s">
+        <v>125</v>
+      </c>
+      <c r="B264" s="95">
+        <v>19</v>
+      </c>
+      <c r="C264" s="95">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="D264" s="96">
+        <v>0.25</v>
+      </c>
+      <c r="E264" s="95">
+        <v>96.3</v>
+      </c>
+      <c r="F264" s="95">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A265" s="97" t="s">
+        <v>124</v>
+      </c>
+      <c r="B265" s="95">
+        <v>17</v>
+      </c>
+      <c r="C265" s="95">
+        <v>10.1</v>
+      </c>
+      <c r="D265" s="96">
+        <v>0.24</v>
+      </c>
+      <c r="E265" s="95">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="F265" s="95">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A266" s="97" t="s">
+        <v>123</v>
+      </c>
+      <c r="B266" s="95">
+        <v>15</v>
+      </c>
+      <c r="C266" s="94">
+        <v>9.99</v>
+      </c>
+      <c r="D266" s="96">
+        <v>0.23</v>
+      </c>
+      <c r="E266" s="95">
+        <v>68.900000000000006</v>
+      </c>
+      <c r="F266" s="95">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A267" s="97" t="s">
+        <v>122</v>
+      </c>
+      <c r="B267" s="95">
+        <v>12</v>
+      </c>
+      <c r="C267" s="94">
+        <v>9.8699999999999992</v>
+      </c>
+      <c r="D267" s="96">
+        <v>0.19</v>
+      </c>
+      <c r="E267" s="95">
+        <v>53.8</v>
+      </c>
+      <c r="F267" s="95">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A268" s="97" t="s">
+        <v>121</v>
+      </c>
+      <c r="B268" s="95">
+        <v>67</v>
+      </c>
+      <c r="C268" s="94">
+        <v>9</v>
+      </c>
+      <c r="D268" s="96">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="E268" s="98">
+        <v>272</v>
+      </c>
+      <c r="F268" s="95">
+        <v>70.099999999999994</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A269" s="97" t="s">
+        <v>120</v>
+      </c>
+      <c r="B269" s="95">
+        <v>58</v>
+      </c>
+      <c r="C269" s="94">
+        <v>8.75</v>
+      </c>
+      <c r="D269" s="96">
+        <v>0.51</v>
+      </c>
+      <c r="E269" s="98">
+        <v>228</v>
+      </c>
+      <c r="F269" s="95">
+        <v>59.8</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A270" s="97" t="s">
+        <v>119</v>
+      </c>
+      <c r="B270" s="95">
+        <v>48</v>
+      </c>
+      <c r="C270" s="94">
+        <v>8.5</v>
+      </c>
+      <c r="D270" s="96">
+        <v>0.4</v>
+      </c>
+      <c r="E270" s="98">
+        <v>184</v>
+      </c>
+      <c r="F270" s="95">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A271" s="97" t="s">
+        <v>118</v>
+      </c>
+      <c r="B271" s="95">
+        <v>40</v>
+      </c>
+      <c r="C271" s="94">
+        <v>8.25</v>
+      </c>
+      <c r="D271" s="96">
+        <v>0.36</v>
+      </c>
+      <c r="E271" s="98">
+        <v>146</v>
+      </c>
+      <c r="F271" s="95">
+        <v>39.799999999999997</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A272" s="97" t="s">
+        <v>117</v>
+      </c>
+      <c r="B272" s="95">
+        <v>35</v>
+      </c>
+      <c r="C272" s="94">
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="D272" s="96">
+        <v>0.31</v>
+      </c>
+      <c r="E272" s="98">
+        <v>127</v>
+      </c>
+      <c r="F272" s="95">
+        <v>34.700000000000003</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A273" s="97" t="s">
+        <v>116</v>
+      </c>
+      <c r="B273" s="95">
+        <v>31</v>
+      </c>
+      <c r="C273" s="94">
+        <v>8</v>
+      </c>
+      <c r="D273" s="96">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="E273" s="98">
+        <v>110</v>
+      </c>
+      <c r="F273" s="95">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A274" s="97" t="s">
+        <v>115</v>
+      </c>
+      <c r="B274" s="95">
+        <v>28</v>
+      </c>
+      <c r="C274" s="94">
+        <v>8.06</v>
+      </c>
+      <c r="D274" s="96">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="E274" s="95">
+        <v>98</v>
+      </c>
+      <c r="F274" s="95">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A275" s="97" t="s">
+        <v>114</v>
+      </c>
+      <c r="B275" s="95">
+        <v>24</v>
+      </c>
+      <c r="C275" s="94">
+        <v>7.93</v>
+      </c>
+      <c r="D275" s="96">
+        <v>0.245</v>
+      </c>
+      <c r="E275" s="95">
+        <v>82.7</v>
+      </c>
+      <c r="F275" s="95">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A276" s="97" t="s">
+        <v>113</v>
+      </c>
+      <c r="B276" s="95">
+        <v>21</v>
+      </c>
+      <c r="C276" s="94">
+        <v>8.2799999999999994</v>
+      </c>
+      <c r="D276" s="96">
+        <v>0.25</v>
+      </c>
+      <c r="E276" s="95">
+        <v>75.3</v>
+      </c>
+      <c r="F276" s="95">
+        <v>20.399999999999999</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A277" s="97" t="s">
+        <v>112</v>
+      </c>
+      <c r="B277" s="95">
+        <v>18</v>
+      </c>
+      <c r="C277" s="94">
+        <v>8.14</v>
+      </c>
+      <c r="D277" s="96">
+        <v>0.23</v>
+      </c>
+      <c r="E277" s="95">
+        <v>61.9</v>
+      </c>
+      <c r="F277" s="95">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A278" s="97" t="s">
+        <v>111</v>
+      </c>
+      <c r="B278" s="95">
+        <v>15</v>
+      </c>
+      <c r="C278" s="94">
+        <v>8.11</v>
+      </c>
+      <c r="D278" s="96">
+        <v>0.245</v>
+      </c>
+      <c r="E278" s="95">
+        <v>48</v>
+      </c>
+      <c r="F278" s="95">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A279" s="97" t="s">
+        <v>110</v>
+      </c>
+      <c r="B279" s="95">
+        <v>13</v>
+      </c>
+      <c r="C279" s="94">
+        <v>7.99</v>
+      </c>
+      <c r="D279" s="96">
+        <v>0.23</v>
+      </c>
+      <c r="E279" s="95">
+        <v>39.6</v>
+      </c>
+      <c r="F279" s="95">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A280" s="97" t="s">
+        <v>109</v>
+      </c>
+      <c r="B280" s="95">
+        <v>10</v>
+      </c>
+      <c r="C280" s="94">
+        <v>7.89</v>
+      </c>
+      <c r="D280" s="96">
+        <v>0.17</v>
+      </c>
+      <c r="E280" s="95">
+        <v>30.8</v>
+      </c>
+      <c r="F280" s="94">
+        <v>8.8699999999999992</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A281" s="97" t="s">
+        <v>108</v>
+      </c>
+      <c r="B281" s="95">
+        <v>25</v>
+      </c>
+      <c r="C281" s="94">
+        <v>6.38</v>
+      </c>
+      <c r="D281" s="96">
+        <v>0.32</v>
+      </c>
+      <c r="E281" s="95">
+        <v>53.4</v>
+      </c>
+      <c r="F281" s="95">
+        <v>18.899999999999999</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A282" s="97" t="s">
+        <v>107</v>
+      </c>
+      <c r="B282" s="95">
+        <v>20</v>
+      </c>
+      <c r="C282" s="94">
+        <v>6.2</v>
+      </c>
+      <c r="D282" s="96">
+        <v>0.26</v>
+      </c>
+      <c r="E282" s="95">
+        <v>41.4</v>
+      </c>
+      <c r="F282" s="95">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A283" s="97" t="s">
+        <v>106</v>
+      </c>
+      <c r="B283" s="95">
+        <v>15</v>
+      </c>
+      <c r="C283" s="94">
+        <v>5.99</v>
+      </c>
+      <c r="D283" s="96">
+        <v>0.23</v>
+      </c>
+      <c r="E283" s="95">
+        <v>29.1</v>
+      </c>
+      <c r="F283" s="95">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A284" s="97" t="s">
+        <v>105</v>
+      </c>
+      <c r="B284" s="95">
+        <v>16</v>
+      </c>
+      <c r="C284" s="94">
+        <v>6.28</v>
+      </c>
+      <c r="D284" s="96">
+        <v>0.26</v>
+      </c>
+      <c r="E284" s="95">
+        <v>32.1</v>
+      </c>
+      <c r="F284" s="95">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A285" s="97" t="s">
+        <v>104</v>
+      </c>
+      <c r="B285" s="95">
+        <v>12</v>
+      </c>
+      <c r="C285" s="94">
+        <v>6.03</v>
+      </c>
+      <c r="D285" s="96">
+        <v>0.23</v>
+      </c>
+      <c r="E285" s="95">
+        <v>22.1</v>
+      </c>
+      <c r="F285" s="94">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A286" s="97" t="s">
+        <v>103</v>
+      </c>
+      <c r="B286" s="94">
+        <v>9</v>
+      </c>
+      <c r="C286" s="94">
+        <v>5.9</v>
+      </c>
+      <c r="D286" s="96">
+        <v>0.17</v>
+      </c>
+      <c r="E286" s="95">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="F286" s="94">
+        <v>6.23</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A287" s="97" t="s">
+        <v>102</v>
+      </c>
+      <c r="B287" s="94">
+        <v>8.5</v>
+      </c>
+      <c r="C287" s="94">
+        <v>5.83</v>
+      </c>
+      <c r="D287" s="96">
+        <v>0.17</v>
+      </c>
+      <c r="E287" s="95">
+        <v>14.9</v>
+      </c>
+      <c r="F287" s="94">
+        <v>5.73</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A288" s="97" t="s">
+        <v>101</v>
+      </c>
+      <c r="B288" s="95">
+        <v>19</v>
+      </c>
+      <c r="C288" s="94">
+        <v>5.15</v>
+      </c>
+      <c r="D288" s="96">
+        <v>0.27</v>
+      </c>
+      <c r="E288" s="95">
+        <v>26.3</v>
+      </c>
+      <c r="F288" s="95">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A289" s="97" t="s">
+        <v>100</v>
+      </c>
+      <c r="B289" s="95">
+        <v>16</v>
+      </c>
+      <c r="C289" s="94">
+        <v>5.01</v>
+      </c>
+      <c r="D289" s="96">
+        <v>0.24</v>
+      </c>
+      <c r="E289" s="95">
+        <v>21.4</v>
+      </c>
+      <c r="F289" s="94">
+        <v>9.6300000000000008</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A290" s="97" t="s">
+        <v>99</v>
+      </c>
+      <c r="B290" s="95">
+        <v>13</v>
+      </c>
+      <c r="C290" s="94">
+        <v>4.16</v>
+      </c>
+      <c r="D290" s="96">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E290" s="95">
+        <v>11.3</v>
+      </c>
+      <c r="F290" s="94">
+        <v>6.28</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B291" s="93"/>
+      <c r="C291" s="93"/>
+      <c r="D291" s="93"/>
+      <c r="E291" s="93"/>
+      <c r="F291" s="93"/>
+    </row>
+    <row r="292" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B292" s="93"/>
+      <c r="C292" s="93"/>
+      <c r="D292" s="93"/>
+      <c r="E292" s="93"/>
+      <c r="F292" s="93"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -6948,14 +14918,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="104" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="62"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="106"/>
     </row>
     <row r="2" spans="1:6" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="48" t="s">
@@ -64612,7 +72582,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet3">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -64625,10 +72595,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="64"/>
+      <c r="B1" s="108"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
@@ -65013,7 +72983,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:N229"/>
@@ -65544,215 +73514,21 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E99BCD4C-E58D-42DD-8328-AD2B9CAF67CB}">
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="27.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="4" width="19.7109375" customWidth="1"/>
-    <col min="5" max="6" width="17.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-    </row>
-    <row r="3" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="65"/>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-    </row>
-    <row r="4" spans="1:6" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="68" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="68" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="68" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="68" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="68" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="68" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A5" s="69" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="71">
-        <v>220</v>
-      </c>
-      <c r="C5" s="74">
-        <v>3</v>
-      </c>
-      <c r="D5" s="74">
-        <v>2</v>
-      </c>
-      <c r="E5" s="75"/>
-      <c r="F5" s="72"/>
-    </row>
-    <row r="6" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A6" s="69" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="71">
-        <v>150</v>
-      </c>
-      <c r="C6" s="74">
-        <v>2</v>
-      </c>
-      <c r="D6" s="74">
-        <v>3</v>
-      </c>
-      <c r="E6" s="75"/>
-      <c r="F6" s="72"/>
-    </row>
-    <row r="7" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A7" s="65"/>
-      <c r="B7" s="65"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
-      <c r="F7" s="65"/>
-    </row>
-    <row r="8" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A8" s="65"/>
-      <c r="B8" s="65"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="65"/>
-    </row>
-    <row r="9" spans="1:6" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A9" s="68" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="68" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="68" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="65"/>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
-    </row>
-    <row r="10" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A10" s="69" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" s="76"/>
-      <c r="C10" s="74">
-        <v>120</v>
-      </c>
-      <c r="D10" s="65"/>
-      <c r="E10" s="65"/>
-      <c r="F10" s="65"/>
-    </row>
-    <row r="11" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A11" s="69" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="76"/>
-      <c r="C11" s="74">
-        <v>120</v>
-      </c>
-      <c r="D11" s="65"/>
-      <c r="E11" s="65"/>
-      <c r="F11" s="65"/>
-    </row>
-    <row r="12" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A12" s="65"/>
-      <c r="B12" s="65"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="65"/>
-      <c r="E12" s="65"/>
-      <c r="F12" s="65"/>
-    </row>
-    <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="65"/>
-      <c r="B13" s="65"/>
-      <c r="C13" s="65"/>
-      <c r="D13" s="65"/>
-      <c r="E13" s="65"/>
-      <c r="F13" s="65"/>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="70" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" s="73"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
-    </row>
-    <row r="15" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A15" s="65"/>
-      <c r="B15" s="65"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="65"/>
-      <c r="E15" s="65"/>
-      <c r="F15" s="65"/>
-    </row>
-    <row r="16" spans="1:6" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A16" s="77" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="77"/>
-      <c r="C16" s="77"/>
-      <c r="D16" s="77"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="77"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="0fb52932-310b-4812-bc91-e280dc622503" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="0fb52932-310b-4812-bc91-e280dc622503" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -65945,14 +73721,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A90C98F-3F03-4FA4-BF92-258CD450675A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F03FBD16-CAC6-438C-A2E6-F114385B594C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -65965,6 +73733,14 @@
     <ds:schemaRef ds:uri="0fb52932-310b-4812-bc91-e280dc622503"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A90C98F-3F03-4FA4-BF92-258CD450675A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
